--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2497" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="356">
   <si>
     <t>Descripcion</t>
   </si>
@@ -1037,6 +1037,9 @@
   </si>
   <si>
     <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
   </si>
   <si>
     <t>2024-04-11</t>
@@ -4432,7 +4435,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4478,90 +4481,64 @@
         <v>190</v>
       </c>
       <c r="F2">
-        <v>8770</v>
+        <v>8500</v>
       </c>
       <c r="G2">
-        <v>877000</v>
+        <v>850000</v>
       </c>
       <c r="H2">
-        <v>150329.3307692307</v>
+        <v>123329.3307692307</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="B3">
-        <v>139</v>
+        <v>42</v>
       </c>
       <c r="C3">
-        <v>14258.8864028777</v>
+        <v>24183.39547619048</v>
       </c>
       <c r="D3">
-        <v>1981985.21</v>
+        <v>1015702.61</v>
       </c>
       <c r="E3" t="s">
         <v>190</v>
       </c>
       <c r="F3">
-        <v>14810</v>
+        <v>24220</v>
       </c>
       <c r="G3">
-        <v>2058590</v>
+        <v>1017240</v>
       </c>
       <c r="H3">
-        <v>76604.79000000004</v>
+        <v>1537.390000000014</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B4">
-        <v>42</v>
+        <v>160170.68</v>
       </c>
       <c r="C4">
-        <v>24183.39547619048</v>
+        <v>12.48667983428678</v>
       </c>
       <c r="D4">
-        <v>1015702.61</v>
+        <v>2000000</v>
       </c>
       <c r="E4" t="s">
         <v>190</v>
       </c>
       <c r="F4">
-        <v>23780</v>
+        <v>12.505889</v>
       </c>
       <c r="G4">
-        <v>998760</v>
+        <v>2003076.74513452</v>
       </c>
       <c r="H4">
-        <v>-16942.60999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B5">
-        <v>160170.68</v>
-      </c>
-      <c r="C5">
-        <v>12.48667983428678</v>
-      </c>
-      <c r="D5">
-        <v>2000000</v>
-      </c>
-      <c r="E5" t="s">
-        <v>190</v>
-      </c>
-      <c r="F5">
-        <v>12.505889</v>
-      </c>
-      <c r="G5">
-        <v>2003076.74513452</v>
-      </c>
-      <c r="H5">
         <v>3076.745134519879</v>
       </c>
     </row>
@@ -4572,7 +4549,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8733,6 +8710,32 @@
       </c>
       <c r="H160">
         <v>51530.33423076922</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B161" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C161" t="s">
+        <v>83</v>
+      </c>
+      <c r="D161" t="s">
+        <v>190</v>
+      </c>
+      <c r="E161">
+        <v>139</v>
+      </c>
+      <c r="F161">
+        <v>14258.8864028777</v>
+      </c>
+      <c r="G161">
+        <v>15034.24086330935</v>
+      </c>
+      <c r="H161">
+        <v>107774.2700000001</v>
       </c>
     </row>
   </sheetData>
@@ -8742,7 +8745,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8799,79 +8802,53 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="B3" s="1">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="C3">
-        <v>139</v>
+        <v>42</v>
       </c>
       <c r="D3">
-        <v>14080</v>
+        <v>23880</v>
       </c>
       <c r="E3">
-        <v>178.886402877697</v>
+        <v>303.3954761904752</v>
       </c>
       <c r="F3">
-        <v>14258.8864028777</v>
+        <v>24183.39547619048</v>
       </c>
       <c r="G3">
-        <v>14442.37680311301</v>
+        <v>24494.59944022999</v>
       </c>
       <c r="H3">
-        <v>1981985.21</v>
+        <v>1015702.61</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B4" s="1">
-        <v>46283</v>
+        <v>46286.80225602954</v>
       </c>
       <c r="C4">
-        <v>42</v>
+        <v>160170.68</v>
       </c>
       <c r="D4">
-        <v>23880</v>
+        <v>12.48667983428678</v>
       </c>
       <c r="E4">
-        <v>303.3954761904752</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>24183.39547619048</v>
+        <v>12.48667983428678</v>
       </c>
       <c r="G4">
-        <v>24494.59944022999</v>
+        <v>12.48667983428678</v>
       </c>
       <c r="H4">
-        <v>1015702.61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B5" s="1">
-        <v>46285.60431405393</v>
-      </c>
-      <c r="C5">
-        <v>160170.68</v>
-      </c>
-      <c r="D5">
-        <v>12.48667983428678</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>12.48667983428678</v>
-      </c>
-      <c r="G5">
-        <v>12.48667983428678</v>
-      </c>
-      <c r="H5">
         <v>2000000</v>
       </c>
     </row>
@@ -8898,7 +8875,7 @@
         <v>242</v>
       </c>
       <c r="B2">
-        <v>536974.775</v>
+        <v>549702.525</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8906,7 +8883,7 @@
         <v>243</v>
       </c>
       <c r="B3">
-        <v>43413.71000000001</v>
+        <v>44686.48</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8914,7 +8891,7 @@
         <v>244</v>
       </c>
       <c r="B4">
-        <v>580388.485</v>
+        <v>594389.005</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8996,7 +8973,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P219"/>
+  <dimension ref="A1:P220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -9666,7 +9643,7 @@
         <v>287</v>
       </c>
       <c r="F14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G14">
         <v>26</v>
@@ -9716,7 +9693,7 @@
         <v>287</v>
       </c>
       <c r="F15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -9766,7 +9743,7 @@
         <v>287</v>
       </c>
       <c r="F16" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -9816,7 +9793,7 @@
         <v>287</v>
       </c>
       <c r="F17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -9866,7 +9843,7 @@
         <v>288</v>
       </c>
       <c r="F18" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G18">
         <v>55</v>
@@ -9916,7 +9893,7 @@
         <v>289</v>
       </c>
       <c r="F19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -9966,7 +9943,7 @@
         <v>289</v>
       </c>
       <c r="F20" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -10016,7 +9993,7 @@
         <v>289</v>
       </c>
       <c r="F21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -10066,7 +10043,7 @@
         <v>289</v>
       </c>
       <c r="F22" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -10116,7 +10093,7 @@
         <v>289</v>
       </c>
       <c r="F23" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -10166,7 +10143,7 @@
         <v>289</v>
       </c>
       <c r="F24" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G24">
         <v>4</v>
@@ -10216,7 +10193,7 @@
         <v>289</v>
       </c>
       <c r="F25" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -10266,7 +10243,7 @@
         <v>290</v>
       </c>
       <c r="F26" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G26">
         <v>9</v>
@@ -10316,7 +10293,7 @@
         <v>290</v>
       </c>
       <c r="F27" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G27">
         <v>6</v>
@@ -10366,7 +10343,7 @@
         <v>290</v>
       </c>
       <c r="F28" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -10416,7 +10393,7 @@
         <v>290</v>
       </c>
       <c r="F29" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -10466,7 +10443,7 @@
         <v>290</v>
       </c>
       <c r="F30" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -10516,7 +10493,7 @@
         <v>290</v>
       </c>
       <c r="F31" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G31">
         <v>7</v>
@@ -10716,7 +10693,7 @@
         <v>293</v>
       </c>
       <c r="F35" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -10766,7 +10743,7 @@
         <v>293</v>
       </c>
       <c r="F36" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G36">
         <v>10</v>
@@ -10816,7 +10793,7 @@
         <v>293</v>
       </c>
       <c r="F37" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -10866,7 +10843,7 @@
         <v>293</v>
       </c>
       <c r="F38" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G38">
         <v>16</v>
@@ -10916,7 +10893,7 @@
         <v>293</v>
       </c>
       <c r="F39" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G39">
         <v>10</v>
@@ -10966,7 +10943,7 @@
         <v>293</v>
       </c>
       <c r="F40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -11016,7 +10993,7 @@
         <v>294</v>
       </c>
       <c r="F41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G41">
         <v>9</v>
@@ -11066,7 +11043,7 @@
         <v>294</v>
       </c>
       <c r="F42" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -11116,7 +11093,7 @@
         <v>294</v>
       </c>
       <c r="F43" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G43">
         <v>21</v>
@@ -12016,7 +11993,7 @@
         <v>296</v>
       </c>
       <c r="F61" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G61">
         <v>4</v>
@@ -12916,7 +12893,7 @@
         <v>298</v>
       </c>
       <c r="F79" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G79">
         <v>5</v>
@@ -13966,7 +13943,7 @@
         <v>305</v>
       </c>
       <c r="F100" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G100">
         <v>297</v>
@@ -14966,7 +14943,7 @@
         <v>310</v>
       </c>
       <c r="F120" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G120">
         <v>100</v>
@@ -16066,7 +16043,7 @@
         <v>312</v>
       </c>
       <c r="F142" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G142">
         <v>33</v>
@@ -19066,7 +19043,7 @@
         <v>328</v>
       </c>
       <c r="F202" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G202">
         <v>90</v>
@@ -19866,7 +19843,7 @@
         <v>337</v>
       </c>
       <c r="F218" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G218">
         <v>100</v>
@@ -19947,6 +19924,56 @@
       </c>
       <c r="P219">
         <v>23880</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16">
+      <c r="A220" t="s">
+        <v>265</v>
+      </c>
+      <c r="B220">
+        <v>10641020</v>
+      </c>
+      <c r="C220" t="s">
+        <v>83</v>
+      </c>
+      <c r="D220" t="s">
+        <v>285</v>
+      </c>
+      <c r="E220" t="s">
+        <v>339</v>
+      </c>
+      <c r="F220" t="s">
+        <v>339</v>
+      </c>
+      <c r="G220">
+        <v>139</v>
+      </c>
+      <c r="H220">
+        <v>15134.9640287769</v>
+      </c>
+      <c r="I220">
+        <v>2103760</v>
+      </c>
+      <c r="J220">
+        <v>1272.77</v>
+      </c>
+      <c r="K220">
+        <v>12727.75</v>
+      </c>
+      <c r="L220">
+        <v>2089759.48</v>
+      </c>
+      <c r="M220" t="s">
+        <v>190</v>
+      </c>
+      <c r="N220" s="1">
+        <v>46286</v>
+      </c>
+      <c r="O220" t="s">
+        <v>83</v>
+      </c>
+      <c r="P220">
+        <v>15134.9640287769</v>
       </c>
     </row>
   </sheetData>
@@ -19969,7 +19996,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B2">
         <v>1000000</v>
@@ -19977,18 +20004,18 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B3">
-        <v>1184719.876087911</v>
+        <v>1292494.146087911</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B4">
-        <v>1213068.255903751</v>
+        <v>1127943.465903751</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2510" uniqueCount="357">
   <si>
     <t>Descripcion</t>
   </si>
@@ -625,7 +625,7 @@
     <t>MELI</t>
   </si>
   <si>
-    <t>BCMMA</t>
+    <t>PESOS LÍQUIDOS</t>
   </si>
   <si>
     <t>Fecha Compra Origen</t>
@@ -1079,6 +1079,9 @@
   </si>
   <si>
     <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
   </si>
   <si>
     <t>Flujo Fondeo Neto</t>
@@ -4469,13 +4472,13 @@
         <v>82</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="C2">
-        <v>7266.706692307693</v>
+        <v>8192.675810936051</v>
       </c>
       <c r="D2">
-        <v>726670.6692307693</v>
+        <v>2719968.369230769</v>
       </c>
       <c r="E2" t="s">
         <v>190</v>
@@ -4484,10 +4487,10 @@
         <v>8500</v>
       </c>
       <c r="G2">
-        <v>850000</v>
+        <v>2822000</v>
       </c>
       <c r="H2">
-        <v>123329.3307692307</v>
+        <v>102031.6307692309</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4521,25 +4524,25 @@
         <v>201</v>
       </c>
       <c r="B4">
-        <v>160170.68</v>
+        <v>2113593.05</v>
       </c>
       <c r="C4">
-        <v>12.48667983428678</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>2000000</v>
+        <v>2113593.05</v>
       </c>
       <c r="E4" t="s">
         <v>190</v>
       </c>
       <c r="F4">
-        <v>12.505889</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>2003076.74513452</v>
+        <v>2113593.05</v>
       </c>
       <c r="H4">
-        <v>3076.745134519879</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8802,54 +8805,54 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="B3" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>232</v>
       </c>
       <c r="D3">
-        <v>23880</v>
+        <v>8535</v>
       </c>
       <c r="E3">
-        <v>303.3954761904752</v>
+        <v>56.80043103448224</v>
       </c>
       <c r="F3">
-        <v>24183.39547619048</v>
+        <v>8591.800431034482</v>
       </c>
       <c r="G3">
-        <v>24494.59944022999</v>
+        <v>8649.361940866287</v>
       </c>
       <c r="H3">
-        <v>1015702.61</v>
+        <v>1993297.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B4" s="1">
-        <v>46286.80225602954</v>
+        <v>46283</v>
       </c>
       <c r="C4">
-        <v>160170.68</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>12.48667983428678</v>
+        <v>23880</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>303.3954761904752</v>
       </c>
       <c r="F4">
-        <v>12.48667983428678</v>
+        <v>24183.39547619048</v>
       </c>
       <c r="G4">
-        <v>12.48667983428678</v>
+        <v>24494.59944022999</v>
       </c>
       <c r="H4">
-        <v>2000000</v>
+        <v>1015702.61</v>
       </c>
     </row>
   </sheetData>
@@ -8875,7 +8878,7 @@
         <v>242</v>
       </c>
       <c r="B2">
-        <v>549702.525</v>
+        <v>561682.255</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8883,7 +8886,7 @@
         <v>243</v>
       </c>
       <c r="B3">
-        <v>44686.48</v>
+        <v>45884.45</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8891,7 +8894,7 @@
         <v>244</v>
       </c>
       <c r="B4">
-        <v>594389.005</v>
+        <v>607566.705</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8973,7 +8976,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P220"/>
+  <dimension ref="A1:P221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -19928,40 +19931,40 @@
     </row>
     <row r="220" spans="1:16">
       <c r="A220" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B220">
-        <v>10641020</v>
+        <v>10668132</v>
       </c>
       <c r="C220" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D220" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E220" t="s">
         <v>339</v>
       </c>
       <c r="F220" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G220">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="H220">
-        <v>15134.9640287769</v>
+        <v>8535</v>
       </c>
       <c r="I220">
-        <v>2103760</v>
+        <v>1980120</v>
       </c>
       <c r="J220">
-        <v>1272.77</v>
+        <v>1197.97</v>
       </c>
       <c r="K220">
-        <v>12727.75</v>
+        <v>11979.73</v>
       </c>
       <c r="L220">
-        <v>2089759.48</v>
+        <v>1993297.7</v>
       </c>
       <c r="M220" t="s">
         <v>190</v>
@@ -19970,9 +19973,59 @@
         <v>46286</v>
       </c>
       <c r="O220" t="s">
+        <v>82</v>
+      </c>
+      <c r="P220">
+        <v>8535</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16">
+      <c r="A221" t="s">
+        <v>265</v>
+      </c>
+      <c r="B221">
+        <v>10641020</v>
+      </c>
+      <c r="C221" t="s">
         <v>83</v>
       </c>
-      <c r="P220">
+      <c r="D221" t="s">
+        <v>285</v>
+      </c>
+      <c r="E221" t="s">
+        <v>339</v>
+      </c>
+      <c r="F221" t="s">
+        <v>339</v>
+      </c>
+      <c r="G221">
+        <v>139</v>
+      </c>
+      <c r="H221">
+        <v>15134.9640287769</v>
+      </c>
+      <c r="I221">
+        <v>2103760</v>
+      </c>
+      <c r="J221">
+        <v>1272.77</v>
+      </c>
+      <c r="K221">
+        <v>12727.75</v>
+      </c>
+      <c r="L221">
+        <v>2089759.48</v>
+      </c>
+      <c r="M221" t="s">
+        <v>190</v>
+      </c>
+      <c r="N221" s="1">
+        <v>46286</v>
+      </c>
+      <c r="O221" t="s">
+        <v>83</v>
+      </c>
+      <c r="P221">
         <v>15134.9640287769</v>
       </c>
     </row>
@@ -19996,15 +20049,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B2">
-        <v>1000000</v>
+        <v>2113593.05</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B3">
         <v>1292494.146087911</v>
@@ -20012,10 +20065,10 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B4">
-        <v>1127943.465903751</v>
+        <v>2217162.070769231</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2510" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="359">
   <si>
     <t>Descripcion</t>
   </si>
@@ -622,6 +622,9 @@
     <t>Ganancia/Perdida NO Realizada ($)</t>
   </si>
   <si>
+    <t>PAMPA ENERGIA</t>
+  </si>
+  <si>
     <t>MELI</t>
   </si>
   <si>
@@ -652,9 +655,6 @@
     <t>CEDEAR BROADCOM INC.</t>
   </si>
   <si>
-    <t>PAMPA ENERGIA</t>
-  </si>
-  <si>
     <t>GRUPO FINANCIERO GALICIA "B"1V.ESC.</t>
   </si>
   <si>
@@ -1042,6 +1042,9 @@
     <t>2026-09-21</t>
   </si>
   <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
     <t>2024-04-11</t>
   </si>
   <si>
@@ -1082,6 +1085,9 @@
   </si>
   <si>
     <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
   </si>
   <si>
     <t>Flujo Fondeo Neto</t>
@@ -4438,7 +4444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4469,54 +4475,54 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="B2">
-        <v>332</v>
+        <v>195</v>
       </c>
       <c r="C2">
-        <v>8192.675810936051</v>
+        <v>5144.007025641025</v>
       </c>
       <c r="D2">
-        <v>2719968.369230769</v>
+        <v>1003081.37</v>
       </c>
       <c r="E2" t="s">
         <v>190</v>
       </c>
       <c r="F2">
-        <v>8500</v>
+        <v>5110</v>
       </c>
       <c r="G2">
-        <v>2822000</v>
+        <v>996450</v>
       </c>
       <c r="H2">
-        <v>102031.6307692309</v>
+        <v>-6631.369999999995</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="B3">
-        <v>42</v>
+        <v>332</v>
       </c>
       <c r="C3">
-        <v>24183.39547619048</v>
+        <v>8192.675810936051</v>
       </c>
       <c r="D3">
-        <v>1015702.61</v>
+        <v>2719968.369230769</v>
       </c>
       <c r="E3" t="s">
         <v>190</v>
       </c>
       <c r="F3">
-        <v>24220</v>
+        <v>8450</v>
       </c>
       <c r="G3">
-        <v>1017240</v>
+        <v>2805400</v>
       </c>
       <c r="H3">
-        <v>1537.390000000014</v>
+        <v>85431.63076923089</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4524,24 +4530,50 @@
         <v>201</v>
       </c>
       <c r="B4">
-        <v>2113593.05</v>
+        <v>42</v>
       </c>
       <c r="C4">
+        <v>24183.39547619048</v>
+      </c>
+      <c r="D4">
+        <v>1015702.61</v>
+      </c>
+      <c r="E4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4">
+        <v>23670</v>
+      </c>
+      <c r="G4">
+        <v>994140</v>
+      </c>
+      <c r="H4">
+        <v>-21562.60999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5">
+        <v>1110511.68</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>2113593.05</v>
-      </c>
-      <c r="E4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F4">
+      <c r="D5">
+        <v>1110511.68</v>
+      </c>
+      <c r="E5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="G4">
-        <v>2113593.05</v>
-      </c>
-      <c r="H4">
+      <c r="G5">
+        <v>1110511.68</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
     </row>
@@ -4557,10 +4589,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -4572,13 +4604,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4589,7 +4621,7 @@
         <v>45391</v>
       </c>
       <c r="C2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D2" t="s">
         <v>190</v>
@@ -4615,7 +4647,7 @@
         <v>45391</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D3" t="s">
         <v>190</v>
@@ -4641,7 +4673,7 @@
         <v>45391</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D4" t="s">
         <v>190</v>
@@ -4667,7 +4699,7 @@
         <v>45414</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D5" t="s">
         <v>190</v>
@@ -4849,7 +4881,7 @@
         <v>45419</v>
       </c>
       <c r="C12" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D12" t="s">
         <v>190</v>
@@ -5057,7 +5089,7 @@
         <v>45443</v>
       </c>
       <c r="C20" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D20" t="s">
         <v>190</v>
@@ -5187,7 +5219,7 @@
         <v>45481</v>
       </c>
       <c r="C25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D25" t="s">
         <v>190</v>
@@ -5265,7 +5297,7 @@
         <v>45509</v>
       </c>
       <c r="C28" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D28" t="s">
         <v>190</v>
@@ -5733,7 +5765,7 @@
         <v>45583</v>
       </c>
       <c r="C46" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D46" t="s">
         <v>190</v>
@@ -5759,7 +5791,7 @@
         <v>45583</v>
       </c>
       <c r="C47" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D47" t="s">
         <v>190</v>
@@ -6773,7 +6805,7 @@
         <v>45674</v>
       </c>
       <c r="C86" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D86" t="s">
         <v>190</v>
@@ -7189,7 +7221,7 @@
         <v>45852</v>
       </c>
       <c r="C102" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D102" t="s">
         <v>190</v>
@@ -7215,7 +7247,7 @@
         <v>45852</v>
       </c>
       <c r="C103" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D103" t="s">
         <v>190</v>
@@ -7241,7 +7273,7 @@
         <v>45852</v>
       </c>
       <c r="C104" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D104" t="s">
         <v>190</v>
@@ -8748,7 +8780,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8779,28 +8811,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="B2" s="1">
-        <v>46197</v>
+        <v>46289</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="D2">
-        <v>7210</v>
+        <v>5110</v>
       </c>
       <c r="E2">
-        <v>56.70669230769272</v>
+        <v>34.00702564102539</v>
       </c>
       <c r="F2">
-        <v>7266.706692307693</v>
+        <v>5144.007025641025</v>
       </c>
       <c r="G2">
-        <v>7324.312452726859</v>
+        <v>5178.469716921776</v>
       </c>
       <c r="H2">
-        <v>726670.6692307693</v>
+        <v>1003081.37</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8808,50 +8840,76 @@
         <v>82</v>
       </c>
       <c r="B3" s="1">
-        <v>46286</v>
+        <v>46197</v>
       </c>
       <c r="C3">
-        <v>232</v>
+        <v>100</v>
       </c>
       <c r="D3">
-        <v>8535</v>
+        <v>7210</v>
       </c>
       <c r="E3">
-        <v>56.80043103448224</v>
+        <v>56.70669230769272</v>
       </c>
       <c r="F3">
-        <v>8591.800431034482</v>
+        <v>7266.706692307693</v>
       </c>
       <c r="G3">
-        <v>8649.361940866287</v>
+        <v>7324.312452726859</v>
       </c>
       <c r="H3">
-        <v>1993297.7</v>
+        <v>726670.6692307693</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="B4" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C4">
+        <v>232</v>
+      </c>
+      <c r="D4">
+        <v>8535</v>
+      </c>
+      <c r="E4">
+        <v>56.80043103448224</v>
+      </c>
+      <c r="F4">
+        <v>8591.800431034482</v>
+      </c>
+      <c r="G4">
+        <v>8649.361940866287</v>
+      </c>
+      <c r="H4">
+        <v>1993297.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" s="1">
         <v>46283</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>42</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>23880</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>303.3954761904752</v>
       </c>
-      <c r="F4">
+      <c r="F5">
         <v>24183.39547619048</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>24494.59944022999</v>
       </c>
-      <c r="H4">
+      <c r="H5">
         <v>1015702.61</v>
       </c>
     </row>
@@ -8878,7 +8936,7 @@
         <v>242</v>
       </c>
       <c r="B2">
-        <v>561682.255</v>
+        <v>567710.775</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8886,7 +8944,7 @@
         <v>243</v>
       </c>
       <c r="B3">
-        <v>45884.45</v>
+        <v>46487.3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8894,7 +8952,7 @@
         <v>244</v>
       </c>
       <c r="B4">
-        <v>607566.705</v>
+        <v>614198.0750000001</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8976,7 +9034,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P221"/>
+  <dimension ref="A1:P222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -9031,7 +9089,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B2">
         <v>2908424</v>
@@ -9073,7 +9131,7 @@
         <v>45390</v>
       </c>
       <c r="O2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P2">
         <v>1960.05</v>
@@ -9281,7 +9339,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B7">
         <v>2908429</v>
@@ -9323,7 +9381,7 @@
         <v>45390</v>
       </c>
       <c r="O7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P7">
         <v>16369.5</v>
@@ -9331,7 +9389,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B8">
         <v>2908430</v>
@@ -9373,7 +9431,7 @@
         <v>45390</v>
       </c>
       <c r="O8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P8">
         <v>35260</v>
@@ -9581,7 +9639,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B13">
         <v>2908435</v>
@@ -9623,7 +9681,7 @@
         <v>45390</v>
       </c>
       <c r="O13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P13">
         <v>35634.5</v>
@@ -9646,7 +9704,7 @@
         <v>287</v>
       </c>
       <c r="F14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G14">
         <v>26</v>
@@ -9681,7 +9739,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B15">
         <v>2967527</v>
@@ -9696,7 +9754,7 @@
         <v>287</v>
       </c>
       <c r="F15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -9723,7 +9781,7 @@
         <v>45391</v>
       </c>
       <c r="O15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P15">
         <v>16524.5</v>
@@ -9731,7 +9789,7 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B16">
         <v>2967528</v>
@@ -9746,7 +9804,7 @@
         <v>287</v>
       </c>
       <c r="F16" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -9773,7 +9831,7 @@
         <v>45391</v>
       </c>
       <c r="O16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P16">
         <v>35645.5</v>
@@ -9781,7 +9839,7 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B17">
         <v>2967529</v>
@@ -9796,7 +9854,7 @@
         <v>287</v>
       </c>
       <c r="F17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -9823,7 +9881,7 @@
         <v>45391</v>
       </c>
       <c r="O17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P17">
         <v>35279.5</v>
@@ -9846,7 +9904,7 @@
         <v>288</v>
       </c>
       <c r="F18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G18">
         <v>55</v>
@@ -9881,7 +9939,7 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B19">
         <v>3611569</v>
@@ -9896,7 +9954,7 @@
         <v>289</v>
       </c>
       <c r="F19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -9923,7 +9981,7 @@
         <v>45414</v>
       </c>
       <c r="O19" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P19">
         <v>2087</v>
@@ -9946,7 +10004,7 @@
         <v>289</v>
       </c>
       <c r="F20" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -9996,7 +10054,7 @@
         <v>289</v>
       </c>
       <c r="F21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -10046,7 +10104,7 @@
         <v>289</v>
       </c>
       <c r="F22" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -10096,7 +10154,7 @@
         <v>289</v>
       </c>
       <c r="F23" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -10146,7 +10204,7 @@
         <v>289</v>
       </c>
       <c r="F24" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G24">
         <v>4</v>
@@ -10196,7 +10254,7 @@
         <v>289</v>
       </c>
       <c r="F25" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -10231,7 +10289,7 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B26">
         <v>3771670</v>
@@ -10246,7 +10304,7 @@
         <v>290</v>
       </c>
       <c r="F26" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G26">
         <v>9</v>
@@ -10273,7 +10331,7 @@
         <v>45419</v>
       </c>
       <c r="O26" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P26">
         <v>2177</v>
@@ -10296,7 +10354,7 @@
         <v>290</v>
       </c>
       <c r="F27" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G27">
         <v>6</v>
@@ -10346,7 +10404,7 @@
         <v>290</v>
       </c>
       <c r="F28" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -10396,7 +10454,7 @@
         <v>290</v>
       </c>
       <c r="F29" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -10446,7 +10504,7 @@
         <v>290</v>
       </c>
       <c r="F30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -10496,7 +10554,7 @@
         <v>290</v>
       </c>
       <c r="F31" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G31">
         <v>7</v>
@@ -10696,7 +10754,7 @@
         <v>293</v>
       </c>
       <c r="F35" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -10746,7 +10804,7 @@
         <v>293</v>
       </c>
       <c r="F36" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G36">
         <v>10</v>
@@ -10796,7 +10854,7 @@
         <v>293</v>
       </c>
       <c r="F37" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -10831,7 +10889,7 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B38">
         <v>4513894</v>
@@ -10846,7 +10904,7 @@
         <v>293</v>
       </c>
       <c r="F38" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G38">
         <v>16</v>
@@ -10873,7 +10931,7 @@
         <v>45443</v>
       </c>
       <c r="O38" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P38">
         <v>2426</v>
@@ -10896,7 +10954,7 @@
         <v>293</v>
       </c>
       <c r="F39" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G39">
         <v>10</v>
@@ -10946,7 +11004,7 @@
         <v>293</v>
       </c>
       <c r="F40" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -10996,7 +11054,7 @@
         <v>294</v>
       </c>
       <c r="F41" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G41">
         <v>9</v>
@@ -11046,7 +11104,7 @@
         <v>294</v>
       </c>
       <c r="F42" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -11096,7 +11154,7 @@
         <v>294</v>
       </c>
       <c r="F43" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G43">
         <v>21</v>
@@ -11231,7 +11289,7 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B46">
         <v>5734647</v>
@@ -11273,7 +11331,7 @@
         <v>45481</v>
       </c>
       <c r="O46" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P46">
         <v>2545.3</v>
@@ -11431,7 +11489,7 @@
     </row>
     <row r="50" spans="1:16">
       <c r="A50" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B50">
         <v>6763852</v>
@@ -11473,7 +11531,7 @@
         <v>45509</v>
       </c>
       <c r="O50" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P50">
         <v>2120</v>
@@ -11996,7 +12054,7 @@
         <v>296</v>
       </c>
       <c r="F61" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G61">
         <v>4</v>
@@ -12031,7 +12089,7 @@
     </row>
     <row r="62" spans="1:16">
       <c r="A62" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B62">
         <v>6926834</v>
@@ -12073,7 +12131,7 @@
         <v>45512</v>
       </c>
       <c r="O62" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P62">
         <v>2520</v>
@@ -12896,7 +12954,7 @@
         <v>298</v>
       </c>
       <c r="F79" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G79">
         <v>5</v>
@@ -13287,7 +13345,7 @@
         <v>7266797</v>
       </c>
       <c r="C87" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D87" t="s">
         <v>284</v>
@@ -13323,7 +13381,7 @@
         <v>45523</v>
       </c>
       <c r="O87" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P87">
         <v>21700</v>
@@ -13481,7 +13539,7 @@
     </row>
     <row r="91" spans="1:16">
       <c r="A91" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B91">
         <v>9247453</v>
@@ -13523,7 +13581,7 @@
         <v>45583</v>
       </c>
       <c r="O91" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P91">
         <v>3240</v>
@@ -13946,7 +14004,7 @@
         <v>305</v>
       </c>
       <c r="F100" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G100">
         <v>297</v>
@@ -14946,7 +15004,7 @@
         <v>310</v>
       </c>
       <c r="F120" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G120">
         <v>100</v>
@@ -15537,7 +15595,7 @@
         <v>649634</v>
       </c>
       <c r="C132" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D132" t="s">
         <v>285</v>
@@ -15573,7 +15631,7 @@
         <v>45674</v>
       </c>
       <c r="O132" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P132">
         <v>18400</v>
@@ -15881,7 +15939,7 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B139">
         <v>3333331</v>
@@ -15923,7 +15981,7 @@
         <v>45755</v>
       </c>
       <c r="O139" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P139">
         <v>3700</v>
@@ -16046,7 +16104,7 @@
         <v>312</v>
       </c>
       <c r="F142" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G142">
         <v>33</v>
@@ -16431,7 +16489,7 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B150">
         <v>6004728</v>
@@ -16473,7 +16531,7 @@
         <v>45849</v>
       </c>
       <c r="O150" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P150">
         <v>3520</v>
@@ -16481,7 +16539,7 @@
     </row>
     <row r="151" spans="1:16">
       <c r="A151" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B151">
         <v>6004729</v>
@@ -16523,7 +16581,7 @@
         <v>45849</v>
       </c>
       <c r="O151" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P151">
         <v>2.79</v>
@@ -16581,7 +16639,7 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B153">
         <v>6069005</v>
@@ -16623,7 +16681,7 @@
         <v>45852</v>
       </c>
       <c r="O153" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P153">
         <v>3695.1428571428</v>
@@ -19046,7 +19104,7 @@
         <v>328</v>
       </c>
       <c r="F202" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G202">
         <v>90</v>
@@ -19846,7 +19904,7 @@
         <v>337</v>
       </c>
       <c r="F218" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G218">
         <v>100</v>
@@ -19887,7 +19945,7 @@
         <v>10583557</v>
       </c>
       <c r="C219" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D219" t="s">
         <v>284</v>
@@ -19923,7 +19981,7 @@
         <v>46283</v>
       </c>
       <c r="O219" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P219">
         <v>23880</v>
@@ -19946,7 +20004,7 @@
         <v>339</v>
       </c>
       <c r="F220" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G220">
         <v>232</v>
@@ -20027,6 +20085,56 @@
       </c>
       <c r="P221">
         <v>15134.9640287769</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16">
+      <c r="A222" t="s">
+        <v>200</v>
+      </c>
+      <c r="B222">
+        <v>10845350</v>
+      </c>
+      <c r="C222" t="s">
+        <v>269</v>
+      </c>
+      <c r="D222" t="s">
+        <v>284</v>
+      </c>
+      <c r="E222" t="s">
+        <v>340</v>
+      </c>
+      <c r="F222" t="s">
+        <v>355</v>
+      </c>
+      <c r="G222">
+        <v>195</v>
+      </c>
+      <c r="H222">
+        <v>5110</v>
+      </c>
+      <c r="I222">
+        <v>996450</v>
+      </c>
+      <c r="J222">
+        <v>602.85</v>
+      </c>
+      <c r="K222">
+        <v>6028.52</v>
+      </c>
+      <c r="L222">
+        <v>1003081.37</v>
+      </c>
+      <c r="M222" t="s">
+        <v>190</v>
+      </c>
+      <c r="N222" s="1">
+        <v>46289</v>
+      </c>
+      <c r="O222" t="s">
+        <v>200</v>
+      </c>
+      <c r="P222">
+        <v>5110</v>
       </c>
     </row>
   </sheetData>
@@ -20049,15 +20157,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B2">
-        <v>2113593.05</v>
+        <v>1110511.68</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B3">
         <v>1292494.146087911</v>
@@ -20065,10 +20173,10 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B4">
-        <v>2217162.070769231</v>
+        <v>1167749.330769231</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="362">
   <si>
     <t>Descripcion</t>
   </si>
@@ -622,198 +622,210 @@
     <t>Ganancia/Perdida NO Realizada ($)</t>
   </si>
   <si>
+    <t>PAMP</t>
+  </si>
+  <si>
+    <t>MELI</t>
+  </si>
+  <si>
+    <t>PESOS LÍQUIDOS</t>
+  </si>
+  <si>
+    <t>DÓLARES LÍQUIDOS</t>
+  </si>
+  <si>
+    <t>CABLE LÍQUIDO</t>
+  </si>
+  <si>
+    <t>Cable</t>
+  </si>
+  <si>
+    <t>Fecha Compra Origen</t>
+  </si>
+  <si>
+    <t>Fecha Venta</t>
+  </si>
+  <si>
+    <t>Precio Compra Promedio</t>
+  </si>
+  <si>
+    <t>Precio Venta Real</t>
+  </si>
+  <si>
+    <t>P&amp;L Realizado ($)</t>
+  </si>
+  <si>
+    <t>CEDEAR QUALCOMM INCORPORATED ESC.</t>
+  </si>
+  <si>
+    <t>CEDEAR TEXAS INSTRUMENTS INC. ESC.</t>
+  </si>
+  <si>
+    <t>CEDEAR BROADCOM INC.</t>
+  </si>
+  <si>
+    <t>GRUPO FINANCIERO GALICIA "B"1V.ESC.</t>
+  </si>
+  <si>
+    <t>T. DE GAS DEL SUR ESC. "B" 1 V.</t>
+  </si>
+  <si>
+    <t>TRANS.GAS DEL NORTE "C" ORD $ ESC</t>
+  </si>
+  <si>
+    <t>BOLSAS Y MERCADOS ARG. $ ORD. (BYMA)</t>
+  </si>
+  <si>
+    <t>CEDEAR TESLA, INC.</t>
+  </si>
+  <si>
+    <t>CEDEAR INTEL CORPORATION ESCRIT.</t>
+  </si>
+  <si>
+    <t>CEDEAR ADVANCED MICRO DEVICES, INC.</t>
+  </si>
+  <si>
+    <t>EDENOR ORDS."B" 1 VOTO ESCRITURALES</t>
+  </si>
+  <si>
+    <t>CEDEAR GOOGLE INC.</t>
+  </si>
+  <si>
+    <t>CEDEAR META PLATFORMS INC.</t>
+  </si>
+  <si>
+    <t>BONO REP. ARGENTINA USD STEP UP 2030</t>
+  </si>
+  <si>
+    <t>CEDEAR THE WALT DISNEY COMPANY</t>
+  </si>
+  <si>
+    <t>BOPREAL S.3 VTO31/05/26 U$S CG</t>
+  </si>
+  <si>
+    <t>CEDEAR AMAZON.COM, INC</t>
+  </si>
+  <si>
+    <t>ALUAR S.A. ORDS 1 VOTO ESCRITURALES</t>
+  </si>
+  <si>
+    <t>ON TECPETROL CL.8 V.24/10/27 U$S CG</t>
+  </si>
+  <si>
+    <t>CEDEAR COCA COLA COMPANY ESCRIT.</t>
+  </si>
+  <si>
+    <t>CEDEAR NOVARTIS AG ADR</t>
+  </si>
+  <si>
+    <t>ON TECPETROL CL.7 VTO22/04/26 U$S CG</t>
+  </si>
+  <si>
+    <t>BONOS DEL TESORO BONCER 2.25% $ 2028</t>
+  </si>
+  <si>
+    <t>BCO. FRANCES ESCRITURALES 1 V.</t>
+  </si>
+  <si>
+    <t>TRANSENER ORDS."B" 1 VOTO ESCRITURALES</t>
+  </si>
+  <si>
+    <t>Fecha de Compra</t>
+  </si>
+  <si>
+    <t>Cantidad Viva</t>
+  </si>
+  <si>
+    <t>Precio Operado</t>
+  </si>
+  <si>
+    <t>Comisión Unitaria</t>
+  </si>
+  <si>
+    <t>Costo Real (Entrada)</t>
+  </si>
+  <si>
+    <t>Breakeven Salida</t>
+  </si>
+  <si>
+    <t>Capital Asignado</t>
+  </si>
+  <si>
+    <t>Metrica</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Comisiones Broker (Arancel)</t>
+  </si>
+  <si>
+    <t>Derechos de Mercado (Bolsa)</t>
+  </si>
+  <si>
+    <t>Total Costos Operativos</t>
+  </si>
+  <si>
+    <t>Fondeos ARS</t>
+  </si>
+  <si>
+    <t>Fondeos USD</t>
+  </si>
+  <si>
+    <t>Fondeos USD Historico ARS</t>
+  </si>
+  <si>
+    <t>Retiros ARS</t>
+  </si>
+  <si>
+    <t>Retiros USD</t>
+  </si>
+  <si>
+    <t>Retiros USD Historico ARS</t>
+  </si>
+  <si>
+    <t>Rentas ARS</t>
+  </si>
+  <si>
+    <t>Rentas USD</t>
+  </si>
+  <si>
+    <t>Rentas USD Historico ARS</t>
+  </si>
+  <si>
+    <t>Especie</t>
+  </si>
+  <si>
+    <t>Num Boleto</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Bruto</t>
+  </si>
+  <si>
+    <t>Costos Mercado</t>
+  </si>
+  <si>
+    <t>Arancel</t>
+  </si>
+  <si>
+    <t>Neto</t>
+  </si>
+  <si>
+    <t>Fecha_Norm</t>
+  </si>
+  <si>
+    <t>Ticker_Norm</t>
+  </si>
+  <si>
+    <t>Precio_Real</t>
+  </si>
+  <si>
     <t>PAMPA ENERGIA</t>
   </si>
   <si>
-    <t>MELI</t>
-  </si>
-  <si>
-    <t>PESOS LÍQUIDOS</t>
-  </si>
-  <si>
-    <t>Fecha Compra Origen</t>
-  </si>
-  <si>
-    <t>Fecha Venta</t>
-  </si>
-  <si>
-    <t>Precio Compra Promedio</t>
-  </si>
-  <si>
-    <t>Precio Venta Real</t>
-  </si>
-  <si>
-    <t>P&amp;L Realizado ($)</t>
-  </si>
-  <si>
-    <t>CEDEAR QUALCOMM INCORPORATED ESC.</t>
-  </si>
-  <si>
-    <t>CEDEAR TEXAS INSTRUMENTS INC. ESC.</t>
-  </si>
-  <si>
-    <t>CEDEAR BROADCOM INC.</t>
-  </si>
-  <si>
-    <t>GRUPO FINANCIERO GALICIA "B"1V.ESC.</t>
-  </si>
-  <si>
-    <t>T. DE GAS DEL SUR ESC. "B" 1 V.</t>
-  </si>
-  <si>
-    <t>TRANS.GAS DEL NORTE "C" ORD $ ESC</t>
-  </si>
-  <si>
-    <t>BOLSAS Y MERCADOS ARG. $ ORD. (BYMA)</t>
-  </si>
-  <si>
-    <t>CEDEAR TESLA, INC.</t>
-  </si>
-  <si>
-    <t>CEDEAR INTEL CORPORATION ESCRIT.</t>
-  </si>
-  <si>
-    <t>CEDEAR ADVANCED MICRO DEVICES, INC.</t>
-  </si>
-  <si>
-    <t>EDENOR ORDS."B" 1 VOTO ESCRITURALES</t>
-  </si>
-  <si>
-    <t>CEDEAR GOOGLE INC.</t>
-  </si>
-  <si>
-    <t>CEDEAR META PLATFORMS INC.</t>
-  </si>
-  <si>
-    <t>BONO REP. ARGENTINA USD STEP UP 2030</t>
-  </si>
-  <si>
-    <t>CEDEAR THE WALT DISNEY COMPANY</t>
-  </si>
-  <si>
-    <t>BOPREAL S.3 VTO31/05/26 U$S CG</t>
-  </si>
-  <si>
-    <t>CEDEAR AMAZON.COM, INC</t>
-  </si>
-  <si>
-    <t>ALUAR S.A. ORDS 1 VOTO ESCRITURALES</t>
-  </si>
-  <si>
-    <t>ON TECPETROL CL.8 V.24/10/27 U$S CG</t>
-  </si>
-  <si>
-    <t>CEDEAR COCA COLA COMPANY ESCRIT.</t>
-  </si>
-  <si>
-    <t>CEDEAR NOVARTIS AG ADR</t>
-  </si>
-  <si>
-    <t>ON TECPETROL CL.7 VTO22/04/26 U$S CG</t>
-  </si>
-  <si>
-    <t>BONOS DEL TESORO BONCER 2.25% $ 2028</t>
-  </si>
-  <si>
-    <t>BCO. FRANCES ESCRITURALES 1 V.</t>
-  </si>
-  <si>
-    <t>TRANSENER ORDS."B" 1 VOTO ESCRITURALES</t>
-  </si>
-  <si>
-    <t>Fecha de Compra</t>
-  </si>
-  <si>
-    <t>Cantidad Viva</t>
-  </si>
-  <si>
-    <t>Precio Operado</t>
-  </si>
-  <si>
-    <t>Comisión Unitaria</t>
-  </si>
-  <si>
-    <t>Costo Real (Entrada)</t>
-  </si>
-  <si>
-    <t>Breakeven Salida</t>
-  </si>
-  <si>
-    <t>Capital Asignado</t>
-  </si>
-  <si>
-    <t>Metrica</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Comisiones Broker (Arancel)</t>
-  </si>
-  <si>
-    <t>Derechos de Mercado (Bolsa)</t>
-  </si>
-  <si>
-    <t>Total Costos Operativos</t>
-  </si>
-  <si>
-    <t>Fondeos ARS</t>
-  </si>
-  <si>
-    <t>Fondeos USD</t>
-  </si>
-  <si>
-    <t>Fondeos USD Historico ARS</t>
-  </si>
-  <si>
-    <t>Retiros ARS</t>
-  </si>
-  <si>
-    <t>Retiros USD</t>
-  </si>
-  <si>
-    <t>Retiros USD Historico ARS</t>
-  </si>
-  <si>
-    <t>Rentas ARS</t>
-  </si>
-  <si>
-    <t>Rentas USD</t>
-  </si>
-  <si>
-    <t>Rentas USD Historico ARS</t>
-  </si>
-  <si>
-    <t>Especie</t>
-  </si>
-  <si>
-    <t>Num Boleto</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Bruto</t>
-  </si>
-  <si>
-    <t>Costos Mercado</t>
-  </si>
-  <si>
-    <t>Arancel</t>
-  </si>
-  <si>
-    <t>Neto</t>
-  </si>
-  <si>
-    <t>Fecha_Norm</t>
-  </si>
-  <si>
-    <t>Ticker_Norm</t>
-  </si>
-  <si>
-    <t>Precio_Real</t>
-  </si>
-  <si>
     <t>YPF S.A. ESCRIT. "D" 1 VOTO</t>
   </si>
   <si>
@@ -827,9 +839,6 @@
   </si>
   <si>
     <t>CEDEAR MERCADOLIBRE INC.</t>
-  </si>
-  <si>
-    <t>PAMP</t>
   </si>
   <si>
     <t>EDN</t>
@@ -4444,7 +4453,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4490,13 +4499,13 @@
         <v>190</v>
       </c>
       <c r="F2">
-        <v>5110</v>
+        <v>5065</v>
       </c>
       <c r="G2">
-        <v>996450</v>
+        <v>987675</v>
       </c>
       <c r="H2">
-        <v>-6631.369999999995</v>
+        <v>-15406.37</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4516,13 +4525,13 @@
         <v>190</v>
       </c>
       <c r="F3">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="G3">
-        <v>2805400</v>
+        <v>2807060</v>
       </c>
       <c r="H3">
-        <v>85431.63076923089</v>
+        <v>87091.63076923089</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4574,6 +4583,58 @@
         <v>1110511.68</v>
       </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6">
+        <v>11.75</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>11.75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>11.75</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7">
+        <v>2.01</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>2.01</v>
+      </c>
+      <c r="E7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>2.01</v>
+      </c>
+      <c r="H7">
         <v>0</v>
       </c>
     </row>
@@ -4589,10 +4650,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -4604,13 +4665,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4621,7 +4682,7 @@
         <v>45391</v>
       </c>
       <c r="C2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D2" t="s">
         <v>190</v>
@@ -4647,7 +4708,7 @@
         <v>45391</v>
       </c>
       <c r="C3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D3" t="s">
         <v>190</v>
@@ -4673,7 +4734,7 @@
         <v>45391</v>
       </c>
       <c r="C4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D4" t="s">
         <v>190</v>
@@ -4725,7 +4786,7 @@
         <v>45414</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D6" t="s">
         <v>190</v>
@@ -4751,7 +4812,7 @@
         <v>45414</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D7" t="s">
         <v>190</v>
@@ -4803,7 +4864,7 @@
         <v>45414</v>
       </c>
       <c r="C9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D9" t="s">
         <v>190</v>
@@ -4829,7 +4890,7 @@
         <v>45414</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D10" t="s">
         <v>190</v>
@@ -4855,7 +4916,7 @@
         <v>45414</v>
       </c>
       <c r="C11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D11" t="s">
         <v>190</v>
@@ -4907,7 +4968,7 @@
         <v>45419</v>
       </c>
       <c r="C13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D13" t="s">
         <v>190</v>
@@ -4933,7 +4994,7 @@
         <v>45419</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D14" t="s">
         <v>190</v>
@@ -4985,7 +5046,7 @@
         <v>45419</v>
       </c>
       <c r="C16" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D16" t="s">
         <v>190</v>
@@ -5011,7 +5072,7 @@
         <v>45419</v>
       </c>
       <c r="C17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D17" t="s">
         <v>190</v>
@@ -5037,7 +5098,7 @@
         <v>45433</v>
       </c>
       <c r="C18" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D18" t="s">
         <v>190</v>
@@ -5063,7 +5124,7 @@
         <v>45433</v>
       </c>
       <c r="C19" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D19" t="s">
         <v>190</v>
@@ -5115,7 +5176,7 @@
         <v>45443</v>
       </c>
       <c r="C21" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D21" t="s">
         <v>190</v>
@@ -5245,7 +5306,7 @@
         <v>45481</v>
       </c>
       <c r="C26" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D26" t="s">
         <v>190</v>
@@ -5323,7 +5384,7 @@
         <v>45509</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D29" t="s">
         <v>190</v>
@@ -5349,7 +5410,7 @@
         <v>45509</v>
       </c>
       <c r="C30" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D30" t="s">
         <v>190</v>
@@ -5375,7 +5436,7 @@
         <v>45509</v>
       </c>
       <c r="C31" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s">
         <v>190</v>
@@ -5427,7 +5488,7 @@
         <v>45509</v>
       </c>
       <c r="C33" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D33" t="s">
         <v>190</v>
@@ -5453,7 +5514,7 @@
         <v>45509</v>
       </c>
       <c r="C34" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D34" t="s">
         <v>190</v>
@@ -5479,7 +5540,7 @@
         <v>45509</v>
       </c>
       <c r="C35" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D35" t="s">
         <v>190</v>
@@ -5505,7 +5566,7 @@
         <v>45509</v>
       </c>
       <c r="C36" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D36" t="s">
         <v>190</v>
@@ -5531,7 +5592,7 @@
         <v>45509</v>
       </c>
       <c r="C37" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D37" t="s">
         <v>190</v>
@@ -5557,7 +5618,7 @@
         <v>45509</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D38" t="s">
         <v>190</v>
@@ -5609,7 +5670,7 @@
         <v>45509</v>
       </c>
       <c r="C40" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D40" t="s">
         <v>190</v>
@@ -5635,7 +5696,7 @@
         <v>45509</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D41" t="s">
         <v>190</v>
@@ -5713,7 +5774,7 @@
         <v>45560</v>
       </c>
       <c r="C44" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D44" t="s">
         <v>190</v>
@@ -5739,7 +5800,7 @@
         <v>45560</v>
       </c>
       <c r="C45" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D45" t="s">
         <v>190</v>
@@ -5817,7 +5878,7 @@
         <v>45583</v>
       </c>
       <c r="C48" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D48" t="s">
         <v>190</v>
@@ -5843,7 +5904,7 @@
         <v>45583</v>
       </c>
       <c r="C49" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D49" t="s">
         <v>190</v>
@@ -5921,7 +5982,7 @@
         <v>45587</v>
       </c>
       <c r="C52" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D52" t="s">
         <v>192</v>
@@ -5947,7 +6008,7 @@
         <v>45587</v>
       </c>
       <c r="C53" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D53" t="s">
         <v>192</v>
@@ -5973,7 +6034,7 @@
         <v>45588</v>
       </c>
       <c r="C54" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D54" t="s">
         <v>190</v>
@@ -5999,7 +6060,7 @@
         <v>45594</v>
       </c>
       <c r="C55" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D55" t="s">
         <v>190</v>
@@ -6025,7 +6086,7 @@
         <v>45594</v>
       </c>
       <c r="C56" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D56" t="s">
         <v>190</v>
@@ -6051,7 +6112,7 @@
         <v>45594</v>
       </c>
       <c r="C57" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D57" t="s">
         <v>190</v>
@@ -6077,7 +6138,7 @@
         <v>45594</v>
       </c>
       <c r="C58" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D58" t="s">
         <v>190</v>
@@ -6129,7 +6190,7 @@
         <v>45597</v>
       </c>
       <c r="C60" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D60" t="s">
         <v>190</v>
@@ -6155,7 +6216,7 @@
         <v>45597</v>
       </c>
       <c r="C61" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D61" t="s">
         <v>190</v>
@@ -6181,7 +6242,7 @@
         <v>45597</v>
       </c>
       <c r="C62" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D62" t="s">
         <v>190</v>
@@ -6207,7 +6268,7 @@
         <v>45616</v>
       </c>
       <c r="C63" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D63" t="s">
         <v>190</v>
@@ -6233,7 +6294,7 @@
         <v>45616</v>
       </c>
       <c r="C64" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D64" t="s">
         <v>190</v>
@@ -6285,7 +6346,7 @@
         <v>45621</v>
       </c>
       <c r="C66" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D66" t="s">
         <v>190</v>
@@ -6311,7 +6372,7 @@
         <v>45621</v>
       </c>
       <c r="C67" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D67" t="s">
         <v>190</v>
@@ -6337,7 +6398,7 @@
         <v>45621</v>
       </c>
       <c r="C68" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D68" t="s">
         <v>190</v>
@@ -6363,7 +6424,7 @@
         <v>45623</v>
       </c>
       <c r="C69" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D69" t="s">
         <v>190</v>
@@ -6467,7 +6528,7 @@
         <v>45632</v>
       </c>
       <c r="C73" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D73" t="s">
         <v>190</v>
@@ -6493,7 +6554,7 @@
         <v>45632</v>
       </c>
       <c r="C74" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D74" t="s">
         <v>190</v>
@@ -6519,7 +6580,7 @@
         <v>45644</v>
       </c>
       <c r="C75" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D75" t="s">
         <v>190</v>
@@ -6545,7 +6606,7 @@
         <v>45644</v>
       </c>
       <c r="C76" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D76" t="s">
         <v>190</v>
@@ -6623,7 +6684,7 @@
         <v>45644</v>
       </c>
       <c r="C79" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D79" t="s">
         <v>190</v>
@@ -6649,7 +6710,7 @@
         <v>45644</v>
       </c>
       <c r="C80" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D80" t="s">
         <v>190</v>
@@ -6701,7 +6762,7 @@
         <v>45652</v>
       </c>
       <c r="C82" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D82" t="s">
         <v>190</v>
@@ -6727,7 +6788,7 @@
         <v>45652</v>
       </c>
       <c r="C83" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D83" t="s">
         <v>190</v>
@@ -6753,7 +6814,7 @@
         <v>45652</v>
       </c>
       <c r="C84" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D84" t="s">
         <v>192</v>
@@ -6779,7 +6840,7 @@
         <v>45666</v>
       </c>
       <c r="C85" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D85" t="s">
         <v>190</v>
@@ -6831,7 +6892,7 @@
         <v>45678</v>
       </c>
       <c r="C87" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D87" t="s">
         <v>192</v>
@@ -6857,7 +6918,7 @@
         <v>45678</v>
       </c>
       <c r="C88" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D88" t="s">
         <v>192</v>
@@ -6883,7 +6944,7 @@
         <v>45678</v>
       </c>
       <c r="C89" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D89" t="s">
         <v>192</v>
@@ -6909,7 +6970,7 @@
         <v>45721</v>
       </c>
       <c r="C90" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D90" t="s">
         <v>190</v>
@@ -6935,7 +6996,7 @@
         <v>45721</v>
       </c>
       <c r="C91" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D91" t="s">
         <v>190</v>
@@ -6961,7 +7022,7 @@
         <v>45736</v>
       </c>
       <c r="C92" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D92" t="s">
         <v>190</v>
@@ -6987,7 +7048,7 @@
         <v>45743</v>
       </c>
       <c r="C93" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D93" t="s">
         <v>190</v>
@@ -7013,7 +7074,7 @@
         <v>45743</v>
       </c>
       <c r="C94" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D94" t="s">
         <v>190</v>
@@ -7039,7 +7100,7 @@
         <v>45751</v>
       </c>
       <c r="C95" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D95" t="s">
         <v>190</v>
@@ -7065,7 +7126,7 @@
         <v>45751</v>
       </c>
       <c r="C96" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D96" t="s">
         <v>190</v>
@@ -7091,7 +7152,7 @@
         <v>45751</v>
       </c>
       <c r="C97" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D97" t="s">
         <v>190</v>
@@ -7143,7 +7204,7 @@
         <v>45761</v>
       </c>
       <c r="C99" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D99" t="s">
         <v>192</v>
@@ -7169,7 +7230,7 @@
         <v>45761</v>
       </c>
       <c r="C100" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D100" t="s">
         <v>192</v>
@@ -7195,7 +7256,7 @@
         <v>45761</v>
       </c>
       <c r="C101" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D101" t="s">
         <v>192</v>
@@ -7351,7 +7412,7 @@
         <v>45862</v>
       </c>
       <c r="C107" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D107" t="s">
         <v>190</v>
@@ -7403,7 +7464,7 @@
         <v>45866</v>
       </c>
       <c r="C109" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D109" t="s">
         <v>190</v>
@@ -7429,7 +7490,7 @@
         <v>45866</v>
       </c>
       <c r="C110" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D110" t="s">
         <v>190</v>
@@ -7455,7 +7516,7 @@
         <v>45868</v>
       </c>
       <c r="C111" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D111" t="s">
         <v>190</v>
@@ -7481,7 +7542,7 @@
         <v>45868</v>
       </c>
       <c r="C112" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D112" t="s">
         <v>190</v>
@@ -7507,7 +7568,7 @@
         <v>45868</v>
       </c>
       <c r="C113" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D113" t="s">
         <v>190</v>
@@ -7533,7 +7594,7 @@
         <v>45873</v>
       </c>
       <c r="C114" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D114" t="s">
         <v>190</v>
@@ -7559,7 +7620,7 @@
         <v>45873</v>
       </c>
       <c r="C115" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D115" t="s">
         <v>190</v>
@@ -7585,7 +7646,7 @@
         <v>45873</v>
       </c>
       <c r="C116" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D116" t="s">
         <v>190</v>
@@ -7611,7 +7672,7 @@
         <v>45873</v>
       </c>
       <c r="C117" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D117" t="s">
         <v>190</v>
@@ -7637,7 +7698,7 @@
         <v>45873</v>
       </c>
       <c r="C118" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D118" t="s">
         <v>190</v>
@@ -7663,7 +7724,7 @@
         <v>45873</v>
       </c>
       <c r="C119" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D119" t="s">
         <v>190</v>
@@ -7741,7 +7802,7 @@
         <v>45894</v>
       </c>
       <c r="C122" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D122" t="s">
         <v>190</v>
@@ -7767,7 +7828,7 @@
         <v>45894</v>
       </c>
       <c r="C123" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D123" t="s">
         <v>190</v>
@@ -7793,7 +7854,7 @@
         <v>45894</v>
       </c>
       <c r="C124" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D124" t="s">
         <v>190</v>
@@ -7819,7 +7880,7 @@
         <v>45894</v>
       </c>
       <c r="C125" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D125" t="s">
         <v>190</v>
@@ -7845,7 +7906,7 @@
         <v>45894</v>
       </c>
       <c r="C126" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D126" t="s">
         <v>190</v>
@@ -7871,7 +7932,7 @@
         <v>45894</v>
       </c>
       <c r="C127" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D127" t="s">
         <v>190</v>
@@ -7897,7 +7958,7 @@
         <v>45894</v>
       </c>
       <c r="C128" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D128" t="s">
         <v>190</v>
@@ -7923,7 +7984,7 @@
         <v>45894</v>
       </c>
       <c r="C129" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D129" t="s">
         <v>190</v>
@@ -7949,7 +8010,7 @@
         <v>45894</v>
       </c>
       <c r="C130" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D130" t="s">
         <v>190</v>
@@ -7975,7 +8036,7 @@
         <v>45894</v>
       </c>
       <c r="C131" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D131" t="s">
         <v>190</v>
@@ -8053,7 +8114,7 @@
         <v>45922</v>
       </c>
       <c r="C134" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D134" t="s">
         <v>190</v>
@@ -8079,7 +8140,7 @@
         <v>45922</v>
       </c>
       <c r="C135" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D135" t="s">
         <v>190</v>
@@ -8105,7 +8166,7 @@
         <v>45922</v>
       </c>
       <c r="C136" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D136" t="s">
         <v>190</v>
@@ -8183,7 +8244,7 @@
         <v>45922</v>
       </c>
       <c r="C139" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D139" t="s">
         <v>190</v>
@@ -8209,7 +8270,7 @@
         <v>45952</v>
       </c>
       <c r="C140" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D140" t="s">
         <v>190</v>
@@ -8547,7 +8608,7 @@
         <v>46182</v>
       </c>
       <c r="C153" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D153" t="s">
         <v>190</v>
@@ -8573,7 +8634,7 @@
         <v>46184</v>
       </c>
       <c r="C154" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D154" t="s">
         <v>190</v>
@@ -8599,7 +8660,7 @@
         <v>46202</v>
       </c>
       <c r="C155" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D155" t="s">
         <v>190</v>
@@ -8625,7 +8686,7 @@
         <v>46204</v>
       </c>
       <c r="C156" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D156" t="s">
         <v>190</v>
@@ -8651,7 +8712,7 @@
         <v>46255</v>
       </c>
       <c r="C157" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D157" t="s">
         <v>190</v>
@@ -8677,7 +8738,7 @@
         <v>46255</v>
       </c>
       <c r="C158" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D158" t="s">
         <v>190</v>
@@ -8788,25 +8849,25 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8925,15 +8986,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B2">
         <v>567710.775</v>
@@ -8941,7 +9002,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B3">
         <v>46487.3</v>
@@ -8949,7 +9010,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B4">
         <v>614198.0750000001</v>
@@ -8957,7 +9018,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B5">
         <v>7139000</v>
@@ -8965,7 +9026,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B6">
         <v>679.1799999999999</v>
@@ -8973,7 +9034,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B7">
         <v>960988.1939999999</v>
@@ -8981,7 +9042,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B8">
         <v>3642008.3</v>
@@ -8989,7 +9050,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B9">
         <v>364.12</v>
@@ -8997,7 +9058,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B10">
         <v>425203.259</v>
@@ -9005,7 +9066,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B11">
         <v>70624.08000000009</v>
@@ -9013,7 +9074,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B12">
         <v>337</v>
@@ -9021,7 +9082,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B13">
         <v>417895.7010000001</v>
@@ -9039,16 +9100,16 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -9063,48 +9124,48 @@
         <v>5</v>
       </c>
       <c r="I1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="K1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M1" t="s">
         <v>7</v>
       </c>
       <c r="N1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="O1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B2">
         <v>2908424</v>
       </c>
       <c r="C2" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G2">
         <v>100</v>
@@ -9139,22 +9200,22 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B3">
         <v>2908425</v>
       </c>
       <c r="C3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G3">
         <v>61</v>
@@ -9181,7 +9242,7 @@
         <v>45390</v>
       </c>
       <c r="O3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="P3">
         <v>1017</v>
@@ -9189,7 +9250,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B4">
         <v>2908426</v>
@@ -9198,13 +9259,13 @@
         <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G4">
         <v>53</v>
@@ -9231,7 +9292,7 @@
         <v>45390</v>
       </c>
       <c r="O4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P4">
         <v>3688</v>
@@ -9239,7 +9300,7 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B5">
         <v>2908427</v>
@@ -9248,13 +9309,13 @@
         <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E5" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -9289,7 +9350,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B6">
         <v>2908428</v>
@@ -9298,13 +9359,13 @@
         <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -9331,7 +9392,7 @@
         <v>45390</v>
       </c>
       <c r="O6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="P6">
         <v>7962.5</v>
@@ -9339,22 +9400,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B7">
         <v>2908429</v>
       </c>
       <c r="C7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D7" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -9381,7 +9442,7 @@
         <v>45390</v>
       </c>
       <c r="O7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P7">
         <v>16369.5</v>
@@ -9389,22 +9450,22 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B8">
         <v>2908430</v>
       </c>
       <c r="C8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F8" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -9431,7 +9492,7 @@
         <v>45390</v>
       </c>
       <c r="O8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="P8">
         <v>35260</v>
@@ -9439,7 +9500,7 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B9">
         <v>2908431</v>
@@ -9448,13 +9509,13 @@
         <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G9">
         <v>41</v>
@@ -9481,7 +9542,7 @@
         <v>45390</v>
       </c>
       <c r="O9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P9">
         <v>2427</v>
@@ -9489,7 +9550,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B10">
         <v>2908432</v>
@@ -9498,13 +9559,13 @@
         <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F10" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -9539,22 +9600,22 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B11">
         <v>2908433</v>
       </c>
       <c r="C11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D11" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -9581,7 +9642,7 @@
         <v>45390</v>
       </c>
       <c r="O11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P11">
         <v>11963</v>
@@ -9589,22 +9650,22 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B12">
         <v>2908434</v>
       </c>
       <c r="C12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D12" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E12" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F12" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -9631,7 +9692,7 @@
         <v>45390</v>
       </c>
       <c r="O12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="P12">
         <v>17674.5</v>
@@ -9639,22 +9700,22 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B13">
         <v>2908435</v>
       </c>
       <c r="C13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E13" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F13" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -9681,7 +9742,7 @@
         <v>45390</v>
       </c>
       <c r="O13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P13">
         <v>35634.5</v>
@@ -9689,7 +9750,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B14">
         <v>2967526</v>
@@ -9698,13 +9759,13 @@
         <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F14" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G14">
         <v>26</v>
@@ -9731,7 +9792,7 @@
         <v>45391</v>
       </c>
       <c r="O14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P14">
         <v>2948</v>
@@ -9739,22 +9800,22 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B15">
         <v>2967527</v>
       </c>
       <c r="C15" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D15" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E15" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F15" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -9781,7 +9842,7 @@
         <v>45391</v>
       </c>
       <c r="O15" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P15">
         <v>16524.5</v>
@@ -9789,22 +9850,22 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B16">
         <v>2967528</v>
       </c>
       <c r="C16" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D16" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E16" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F16" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -9831,7 +9892,7 @@
         <v>45391</v>
       </c>
       <c r="O16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="P16">
         <v>35645.5</v>
@@ -9839,22 +9900,22 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B17">
         <v>2967529</v>
       </c>
       <c r="C17" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F17" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -9881,7 +9942,7 @@
         <v>45391</v>
       </c>
       <c r="O17" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P17">
         <v>35279.5</v>
@@ -9889,7 +9950,7 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B18">
         <v>3014167</v>
@@ -9898,13 +9959,13 @@
         <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E18" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F18" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G18">
         <v>55</v>
@@ -9931,7 +9992,7 @@
         <v>45392</v>
       </c>
       <c r="O18" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P18">
         <v>1459.5</v>
@@ -9939,22 +10000,22 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B19">
         <v>3611569</v>
       </c>
       <c r="C19" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E19" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F19" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -9989,7 +10050,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B20">
         <v>3611570</v>
@@ -9998,13 +10059,13 @@
         <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E20" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F20" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -10031,7 +10092,7 @@
         <v>45414</v>
       </c>
       <c r="O20" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P20">
         <v>3580</v>
@@ -10039,7 +10100,7 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B21">
         <v>3611571</v>
@@ -10048,13 +10109,13 @@
         <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E21" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F21" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -10081,7 +10142,7 @@
         <v>45414</v>
       </c>
       <c r="O21" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P21">
         <v>4150</v>
@@ -10089,7 +10150,7 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B22">
         <v>3611572</v>
@@ -10098,13 +10159,13 @@
         <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E22" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F22" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -10139,7 +10200,7 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B23">
         <v>3611573</v>
@@ -10148,13 +10209,13 @@
         <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E23" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F23" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -10181,7 +10242,7 @@
         <v>45414</v>
       </c>
       <c r="O23" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P23">
         <v>2509</v>
@@ -10189,7 +10250,7 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B24">
         <v>3611574</v>
@@ -10198,13 +10259,13 @@
         <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E24" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F24" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G24">
         <v>4</v>
@@ -10231,7 +10292,7 @@
         <v>45414</v>
       </c>
       <c r="O24" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P24">
         <v>1530</v>
@@ -10239,22 +10300,22 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B25">
         <v>3611575</v>
       </c>
       <c r="C25" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E25" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F25" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -10281,7 +10342,7 @@
         <v>45414</v>
       </c>
       <c r="O25" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P25">
         <v>13431.5</v>
@@ -10289,22 +10350,22 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B26">
         <v>3771670</v>
       </c>
       <c r="C26" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E26" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F26" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G26">
         <v>9</v>
@@ -10339,7 +10400,7 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B27">
         <v>3771671</v>
@@ -10348,13 +10409,13 @@
         <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F27" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G27">
         <v>6</v>
@@ -10381,7 +10442,7 @@
         <v>45419</v>
       </c>
       <c r="O27" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P27">
         <v>3972</v>
@@ -10389,7 +10450,7 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B28">
         <v>3771672</v>
@@ -10398,13 +10459,13 @@
         <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F28" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -10431,7 +10492,7 @@
         <v>45419</v>
       </c>
       <c r="O28" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P28">
         <v>4219</v>
@@ -10439,7 +10500,7 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B29">
         <v>3771673</v>
@@ -10448,13 +10509,13 @@
         <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E29" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F29" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -10489,7 +10550,7 @@
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B30">
         <v>3771674</v>
@@ -10498,13 +10559,13 @@
         <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E30" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F30" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -10531,7 +10592,7 @@
         <v>45419</v>
       </c>
       <c r="O30" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P30">
         <v>2570</v>
@@ -10539,7 +10600,7 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B31">
         <v>3771675</v>
@@ -10548,13 +10609,13 @@
         <v>97</v>
       </c>
       <c r="D31" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F31" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G31">
         <v>7</v>
@@ -10581,7 +10642,7 @@
         <v>45419</v>
       </c>
       <c r="O31" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P31">
         <v>1673.5</v>
@@ -10589,7 +10650,7 @@
     </row>
     <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B32">
         <v>4185042</v>
@@ -10598,13 +10659,13 @@
         <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E32" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F32" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -10631,7 +10692,7 @@
         <v>45433</v>
       </c>
       <c r="O32" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="P32">
         <v>7377.1666666666</v>
@@ -10639,22 +10700,22 @@
     </row>
     <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B33">
         <v>4185043</v>
       </c>
       <c r="C33" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D33" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E33" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -10681,7 +10742,7 @@
         <v>45433</v>
       </c>
       <c r="O33" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="P33">
         <v>19290</v>
@@ -10689,7 +10750,7 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B34">
         <v>4257961</v>
@@ -10698,13 +10759,13 @@
         <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E34" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F34" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G34">
         <v>120</v>
@@ -10731,7 +10792,7 @@
         <v>45435</v>
       </c>
       <c r="O34" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P34">
         <v>676.5</v>
@@ -10739,7 +10800,7 @@
     </row>
     <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B35">
         <v>4513896</v>
@@ -10748,13 +10809,13 @@
         <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E35" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F35" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -10789,7 +10850,7 @@
     </row>
     <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B36">
         <v>4513897</v>
@@ -10798,13 +10859,13 @@
         <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E36" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F36" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G36">
         <v>10</v>
@@ -10831,7 +10892,7 @@
         <v>45443</v>
       </c>
       <c r="O36" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P36">
         <v>3643.5</v>
@@ -10839,7 +10900,7 @@
     </row>
     <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B37">
         <v>4513898</v>
@@ -10848,13 +10909,13 @@
         <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E37" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F37" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -10881,7 +10942,7 @@
         <v>45443</v>
       </c>
       <c r="O37" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="P37">
         <v>23550</v>
@@ -10889,22 +10950,22 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B38">
         <v>4513894</v>
       </c>
       <c r="C38" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D38" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E38" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F38" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G38">
         <v>16</v>
@@ -10939,7 +11000,7 @@
     </row>
     <row r="39" spans="1:16">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B39">
         <v>4513895</v>
@@ -10948,13 +11009,13 @@
         <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E39" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F39" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G39">
         <v>10</v>
@@ -10981,7 +11042,7 @@
         <v>45443</v>
       </c>
       <c r="O39" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P39">
         <v>4842</v>
@@ -10989,7 +11050,7 @@
     </row>
     <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B40">
         <v>4513899</v>
@@ -10998,13 +11059,13 @@
         <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E40" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F40" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -11039,7 +11100,7 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B41">
         <v>5532541</v>
@@ -11048,13 +11109,13 @@
         <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E41" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F41" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G41">
         <v>9</v>
@@ -11081,7 +11142,7 @@
         <v>45475</v>
       </c>
       <c r="O41" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P41">
         <v>4524</v>
@@ -11089,7 +11150,7 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B42">
         <v>5532543</v>
@@ -11098,13 +11159,13 @@
         <v>95</v>
       </c>
       <c r="D42" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E42" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F42" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -11131,7 +11192,7 @@
         <v>45475</v>
       </c>
       <c r="O42" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="P42">
         <v>1082.5</v>
@@ -11139,7 +11200,7 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B43">
         <v>5532542</v>
@@ -11148,13 +11209,13 @@
         <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E43" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F43" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G43">
         <v>21</v>
@@ -11189,22 +11250,22 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B44">
         <v>5744896</v>
       </c>
       <c r="C44" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D44" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E44" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F44" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -11231,7 +11292,7 @@
         <v>45481</v>
       </c>
       <c r="O44" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P44">
         <v>23480</v>
@@ -11239,19 +11300,19 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B45">
         <v>5773473</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D45" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E45" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F45" t="s">
         <v>173</v>
@@ -11281,7 +11342,7 @@
         <v>45481</v>
       </c>
       <c r="O45" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="P45">
         <v>37757</v>
@@ -11289,22 +11350,22 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B46">
         <v>5734647</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D46" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E46" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F46" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G46">
         <v>15</v>
@@ -11339,7 +11400,7 @@
     </row>
     <row r="47" spans="1:16">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B47">
         <v>5734648</v>
@@ -11348,13 +11409,13 @@
         <v>87</v>
       </c>
       <c r="D47" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E47" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F47" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G47">
         <v>7</v>
@@ -11381,7 +11442,7 @@
         <v>45481</v>
       </c>
       <c r="O47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P47">
         <v>5026</v>
@@ -11389,7 +11450,7 @@
     </row>
     <row r="48" spans="1:16">
       <c r="A48" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B48">
         <v>5734649</v>
@@ -11398,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="D48" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E48" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F48" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -11439,7 +11500,7 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B49">
         <v>6763862</v>
@@ -11448,13 +11509,13 @@
         <v>86</v>
       </c>
       <c r="D49" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E49" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F49" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G49">
         <v>1416</v>
@@ -11481,7 +11542,7 @@
         <v>45509</v>
       </c>
       <c r="O49" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P49">
         <v>617.2</v>
@@ -11489,22 +11550,22 @@
     </row>
     <row r="50" spans="1:16">
       <c r="A50" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B50">
         <v>6763852</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D50" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E50" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F50" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G50">
         <v>46</v>
@@ -11539,22 +11600,22 @@
     </row>
     <row r="51" spans="1:16">
       <c r="A51" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B51">
         <v>6763853</v>
       </c>
       <c r="C51" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D51" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E51" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F51" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G51">
         <v>61</v>
@@ -11581,7 +11642,7 @@
         <v>45509</v>
       </c>
       <c r="O51" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="P51">
         <v>984</v>
@@ -11589,7 +11650,7 @@
     </row>
     <row r="52" spans="1:16">
       <c r="A52" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B52">
         <v>6763854</v>
@@ -11598,13 +11659,13 @@
         <v>84</v>
       </c>
       <c r="D52" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E52" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F52" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G52">
         <v>16</v>
@@ -11631,7 +11692,7 @@
         <v>45509</v>
       </c>
       <c r="O52" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P52">
         <v>3340</v>
@@ -11639,7 +11700,7 @@
     </row>
     <row r="53" spans="1:16">
       <c r="A53" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B53">
         <v>6763855</v>
@@ -11648,13 +11709,13 @@
         <v>87</v>
       </c>
       <c r="D53" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E53" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F53" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G53">
         <v>26</v>
@@ -11681,7 +11742,7 @@
         <v>45509</v>
       </c>
       <c r="O53" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P53">
         <v>3955</v>
@@ -11689,7 +11750,7 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B54">
         <v>6763856</v>
@@ -11698,13 +11759,13 @@
         <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E54" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F54" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -11739,7 +11800,7 @@
     </row>
     <row r="55" spans="1:16">
       <c r="A55" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B55">
         <v>6763857</v>
@@ -11748,13 +11809,13 @@
         <v>88</v>
       </c>
       <c r="D55" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E55" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F55" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G55">
         <v>38</v>
@@ -11781,7 +11842,7 @@
         <v>45509</v>
       </c>
       <c r="O55" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P55">
         <v>2560</v>
@@ -11789,7 +11850,7 @@
     </row>
     <row r="56" spans="1:16">
       <c r="A56" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B56">
         <v>6763858</v>
@@ -11798,13 +11859,13 @@
         <v>90</v>
       </c>
       <c r="D56" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E56" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F56" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G56">
         <v>19</v>
@@ -11831,7 +11892,7 @@
         <v>45509</v>
       </c>
       <c r="O56" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P56">
         <v>3755</v>
@@ -11839,7 +11900,7 @@
     </row>
     <row r="57" spans="1:16">
       <c r="A57" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B57">
         <v>6763859</v>
@@ -11848,13 +11909,13 @@
         <v>97</v>
       </c>
       <c r="D57" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E57" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F57" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G57">
         <v>220</v>
@@ -11881,7 +11942,7 @@
         <v>45509</v>
       </c>
       <c r="O57" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P57">
         <v>273</v>
@@ -11889,7 +11950,7 @@
     </row>
     <row r="58" spans="1:16">
       <c r="A58" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B58">
         <v>6763860</v>
@@ -11898,13 +11959,13 @@
         <v>94</v>
       </c>
       <c r="D58" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E58" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F58" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -11931,7 +11992,7 @@
         <v>45509</v>
       </c>
       <c r="O58" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="P58">
         <v>26275</v>
@@ -11939,7 +12000,7 @@
     </row>
     <row r="59" spans="1:16">
       <c r="A59" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B59">
         <v>6763861</v>
@@ -11948,13 +12009,13 @@
         <v>83</v>
       </c>
       <c r="D59" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E59" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F59" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G59">
         <v>29</v>
@@ -11989,7 +12050,7 @@
     </row>
     <row r="60" spans="1:16">
       <c r="A60" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B60">
         <v>6763863</v>
@@ -11998,13 +12059,13 @@
         <v>86</v>
       </c>
       <c r="D60" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E60" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F60" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G60">
         <v>1536</v>
@@ -12031,7 +12092,7 @@
         <v>45509</v>
       </c>
       <c r="O60" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P60">
         <v>617.3671875</v>
@@ -12039,7 +12100,7 @@
     </row>
     <row r="61" spans="1:16">
       <c r="A61" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B61">
         <v>6803479</v>
@@ -12048,13 +12109,13 @@
         <v>93</v>
       </c>
       <c r="D61" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E61" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F61" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G61">
         <v>4</v>
@@ -12089,22 +12150,22 @@
     </row>
     <row r="62" spans="1:16">
       <c r="A62" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B62">
         <v>6926834</v>
       </c>
       <c r="C62" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D62" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E62" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F62" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G62">
         <v>10</v>
@@ -12139,22 +12200,22 @@
     </row>
     <row r="63" spans="1:16">
       <c r="A63" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B63">
         <v>6926835</v>
       </c>
       <c r="C63" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D63" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E63" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F63" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G63">
         <v>38</v>
@@ -12181,7 +12242,7 @@
         <v>45512</v>
       </c>
       <c r="O63" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="P63">
         <v>1050</v>
@@ -12189,7 +12250,7 @@
     </row>
     <row r="64" spans="1:16">
       <c r="A64" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B64">
         <v>6926836</v>
@@ -12198,13 +12259,13 @@
         <v>84</v>
       </c>
       <c r="D64" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E64" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F64" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -12231,7 +12292,7 @@
         <v>45512</v>
       </c>
       <c r="O64" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P64">
         <v>3955</v>
@@ -12239,7 +12300,7 @@
     </row>
     <row r="65" spans="1:16">
       <c r="A65" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B65">
         <v>6926837</v>
@@ -12248,13 +12309,13 @@
         <v>87</v>
       </c>
       <c r="D65" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E65" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F65" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G65">
         <v>6</v>
@@ -12281,7 +12342,7 @@
         <v>45512</v>
       </c>
       <c r="O65" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P65">
         <v>4640</v>
@@ -12289,7 +12350,7 @@
     </row>
     <row r="66" spans="1:16">
       <c r="A66" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B66">
         <v>6926838</v>
@@ -12298,13 +12359,13 @@
         <v>82</v>
       </c>
       <c r="D66" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E66" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F66" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G66">
         <v>2</v>
@@ -12339,7 +12400,7 @@
     </row>
     <row r="67" spans="1:16">
       <c r="A67" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B67">
         <v>6926839</v>
@@ -12348,13 +12409,13 @@
         <v>93</v>
       </c>
       <c r="D67" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E67" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F67" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G67">
         <v>2</v>
@@ -12389,7 +12450,7 @@
     </row>
     <row r="68" spans="1:16">
       <c r="A68" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B68">
         <v>6926840</v>
@@ -12398,13 +12459,13 @@
         <v>90</v>
       </c>
       <c r="D68" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E68" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F68" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G68">
         <v>10</v>
@@ -12431,7 +12492,7 @@
         <v>45512</v>
       </c>
       <c r="O68" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P68">
         <v>3720</v>
@@ -12439,7 +12500,7 @@
     </row>
     <row r="69" spans="1:16">
       <c r="A69" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B69">
         <v>6926841</v>
@@ -12448,13 +12509,13 @@
         <v>97</v>
       </c>
       <c r="D69" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E69" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F69" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G69">
         <v>173</v>
@@ -12481,7 +12542,7 @@
         <v>45512</v>
       </c>
       <c r="O69" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P69">
         <v>288.1531791907</v>
@@ -12489,7 +12550,7 @@
     </row>
     <row r="70" spans="1:16">
       <c r="A70" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B70">
         <v>6926842</v>
@@ -12498,13 +12559,13 @@
         <v>94</v>
       </c>
       <c r="D70" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E70" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F70" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -12531,7 +12592,7 @@
         <v>45512</v>
       </c>
       <c r="O70" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="P70">
         <v>27700</v>
@@ -12539,7 +12600,7 @@
     </row>
     <row r="71" spans="1:16">
       <c r="A71" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B71">
         <v>6926843</v>
@@ -12548,13 +12609,13 @@
         <v>83</v>
       </c>
       <c r="D71" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E71" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F71" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G71">
         <v>8</v>
@@ -12589,7 +12650,7 @@
     </row>
     <row r="72" spans="1:16">
       <c r="A72" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B72">
         <v>6957362</v>
@@ -12598,13 +12659,13 @@
         <v>88</v>
       </c>
       <c r="D72" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E72" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F72" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G72">
         <v>7</v>
@@ -12631,7 +12692,7 @@
         <v>45512</v>
       </c>
       <c r="O72" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P72">
         <v>2880</v>
@@ -12639,22 +12700,22 @@
     </row>
     <row r="73" spans="1:16">
       <c r="A73" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B73">
         <v>6986017</v>
       </c>
       <c r="C73" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D73" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E73" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F73" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G73">
         <v>95</v>
@@ -12681,7 +12742,7 @@
         <v>45513</v>
       </c>
       <c r="O73" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P73">
         <v>928.6736842105</v>
@@ -12689,7 +12750,7 @@
     </row>
     <row r="74" spans="1:16">
       <c r="A74" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B74">
         <v>6986018</v>
@@ -12698,13 +12759,13 @@
         <v>87</v>
       </c>
       <c r="D74" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E74" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F74" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G74">
         <v>3</v>
@@ -12731,7 +12792,7 @@
         <v>45513</v>
       </c>
       <c r="O74" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P74">
         <v>4935</v>
@@ -12739,7 +12800,7 @@
     </row>
     <row r="75" spans="1:16">
       <c r="A75" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B75">
         <v>6986019</v>
@@ -12748,13 +12809,13 @@
         <v>88</v>
       </c>
       <c r="D75" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E75" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F75" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G75">
         <v>29</v>
@@ -12781,7 +12842,7 @@
         <v>45513</v>
       </c>
       <c r="O75" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P75">
         <v>2930</v>
@@ -12789,7 +12850,7 @@
     </row>
     <row r="76" spans="1:16">
       <c r="A76" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B76">
         <v>6986020</v>
@@ -12798,13 +12859,13 @@
         <v>93</v>
       </c>
       <c r="D76" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E76" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F76" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -12839,7 +12900,7 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B77">
         <v>6986021</v>
@@ -12848,13 +12909,13 @@
         <v>97</v>
       </c>
       <c r="D77" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E77" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F77" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G77">
         <v>173</v>
@@ -12881,7 +12942,7 @@
         <v>45513</v>
       </c>
       <c r="O77" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P77">
         <v>284</v>
@@ -12889,22 +12950,22 @@
     </row>
     <row r="78" spans="1:16">
       <c r="A78" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B78">
         <v>6986022</v>
       </c>
       <c r="C78" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D78" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E78" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F78" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -12931,7 +12992,7 @@
         <v>45513</v>
       </c>
       <c r="O78" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P78">
         <v>17275</v>
@@ -12939,7 +13000,7 @@
     </row>
     <row r="79" spans="1:16">
       <c r="A79" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B79">
         <v>7000884</v>
@@ -12948,13 +13009,13 @@
         <v>90</v>
       </c>
       <c r="D79" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E79" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F79" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G79">
         <v>5</v>
@@ -12981,7 +13042,7 @@
         <v>45513</v>
       </c>
       <c r="O79" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P79">
         <v>3625</v>
@@ -12989,7 +13050,7 @@
     </row>
     <row r="80" spans="1:16">
       <c r="A80" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B80">
         <v>7071991</v>
@@ -12998,13 +13059,13 @@
         <v>91</v>
       </c>
       <c r="D80" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E80" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F80" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G80">
         <v>2</v>
@@ -13031,7 +13092,7 @@
         <v>45517</v>
       </c>
       <c r="O80" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P80">
         <v>17450</v>
@@ -13039,22 +13100,22 @@
     </row>
     <row r="81" spans="1:16">
       <c r="A81" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B81">
         <v>7071992</v>
       </c>
       <c r="C81" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D81" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E81" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F81" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G81">
         <v>2</v>
@@ -13081,7 +13142,7 @@
         <v>45517</v>
       </c>
       <c r="O81" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P81">
         <v>9140</v>
@@ -13089,7 +13150,7 @@
     </row>
     <row r="82" spans="1:16">
       <c r="A82" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B82">
         <v>7071993</v>
@@ -13098,13 +13159,13 @@
         <v>92</v>
       </c>
       <c r="D82" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E82" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F82" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G82">
         <v>2</v>
@@ -13139,22 +13200,22 @@
     </row>
     <row r="83" spans="1:16">
       <c r="A83" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B83">
         <v>7071994</v>
       </c>
       <c r="C83" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D83" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E83" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F83" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G83">
         <v>20</v>
@@ -13181,7 +13242,7 @@
         <v>45517</v>
       </c>
       <c r="O83" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P83">
         <v>1490</v>
@@ -13189,22 +13250,22 @@
     </row>
     <row r="84" spans="1:16">
       <c r="A84" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B84">
         <v>7071995</v>
       </c>
       <c r="C84" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D84" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E84" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F84" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G84">
         <v>2</v>
@@ -13231,7 +13292,7 @@
         <v>45517</v>
       </c>
       <c r="O84" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="P84">
         <v>17925</v>
@@ -13239,7 +13300,7 @@
     </row>
     <row r="85" spans="1:16">
       <c r="A85" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B85">
         <v>7071996</v>
@@ -13248,13 +13309,13 @@
         <v>86</v>
       </c>
       <c r="D85" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E85" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F85" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G85">
         <v>50</v>
@@ -13281,7 +13342,7 @@
         <v>45517</v>
       </c>
       <c r="O85" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P85">
         <v>629.8</v>
@@ -13289,7 +13350,7 @@
     </row>
     <row r="86" spans="1:16">
       <c r="A86" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B86">
         <v>7223951</v>
@@ -13298,7 +13359,7 @@
         <v>83</v>
       </c>
       <c r="D86" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E86" t="s">
         <v>171</v>
@@ -13339,7 +13400,7 @@
     </row>
     <row r="87" spans="1:16">
       <c r="A87" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B87">
         <v>7266797</v>
@@ -13348,13 +13409,13 @@
         <v>201</v>
       </c>
       <c r="D87" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E87" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F87" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G87">
         <v>9</v>
@@ -13389,7 +13450,7 @@
     </row>
     <row r="88" spans="1:16">
       <c r="A88" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B88">
         <v>7268048</v>
@@ -13398,13 +13459,13 @@
         <v>83</v>
       </c>
       <c r="D88" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E88" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F88" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G88">
         <v>35</v>
@@ -13439,7 +13500,7 @@
     </row>
     <row r="89" spans="1:16">
       <c r="A89" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B89">
         <v>8479354</v>
@@ -13448,13 +13509,13 @@
         <v>88</v>
       </c>
       <c r="D89" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E89" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F89" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G89">
         <v>15</v>
@@ -13481,7 +13542,7 @@
         <v>45560</v>
       </c>
       <c r="O89" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P89">
         <v>3270</v>
@@ -13489,7 +13550,7 @@
     </row>
     <row r="90" spans="1:16">
       <c r="A90" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B90">
         <v>9265990</v>
@@ -13498,13 +13559,13 @@
         <v>92</v>
       </c>
       <c r="D90" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E90" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F90" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G90">
         <v>2</v>
@@ -13539,22 +13600,22 @@
     </row>
     <row r="91" spans="1:16">
       <c r="A91" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B91">
         <v>9247453</v>
       </c>
       <c r="C91" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D91" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E91" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F91" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G91">
         <v>18</v>
@@ -13589,7 +13650,7 @@
     </row>
     <row r="92" spans="1:16">
       <c r="A92" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B92">
         <v>9247454</v>
@@ -13598,13 +13659,13 @@
         <v>84</v>
       </c>
       <c r="D92" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E92" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F92" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G92">
         <v>5</v>
@@ -13631,7 +13692,7 @@
         <v>45583</v>
       </c>
       <c r="O92" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P92">
         <v>5990</v>
@@ -13639,7 +13700,7 @@
     </row>
     <row r="93" spans="1:16">
       <c r="A93" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B93">
         <v>9247455</v>
@@ -13648,13 +13709,13 @@
         <v>97</v>
       </c>
       <c r="D93" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E93" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F93" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G93">
         <v>31</v>
@@ -13681,7 +13742,7 @@
         <v>45583</v>
       </c>
       <c r="O93" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P93">
         <v>317</v>
@@ -13689,7 +13750,7 @@
     </row>
     <row r="94" spans="1:16">
       <c r="A94" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B94">
         <v>9247456</v>
@@ -13698,13 +13759,13 @@
         <v>83</v>
       </c>
       <c r="D94" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E94" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F94" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G94">
         <v>21</v>
@@ -13739,7 +13800,7 @@
     </row>
     <row r="95" spans="1:16">
       <c r="A95" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B95">
         <v>9282036</v>
@@ -13748,13 +13809,13 @@
         <v>86</v>
       </c>
       <c r="D95" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E95" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F95" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G95">
         <v>179</v>
@@ -13781,7 +13842,7 @@
         <v>45586</v>
       </c>
       <c r="O95" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P95">
         <v>720.5</v>
@@ -13789,19 +13850,19 @@
     </row>
     <row r="96" spans="1:16">
       <c r="A96" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B96">
         <v>9308525</v>
       </c>
       <c r="C96" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D96" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E96" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F96" t="s">
         <v>163</v>
@@ -13831,7 +13892,7 @@
         <v>45586</v>
       </c>
       <c r="O96" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="P96">
         <v>1192</v>
@@ -13839,7 +13900,7 @@
     </row>
     <row r="97" spans="1:16">
       <c r="A97" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B97">
         <v>9326372</v>
@@ -13848,7 +13909,7 @@
         <v>86</v>
       </c>
       <c r="D97" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E97" t="s">
         <v>163</v>
@@ -13881,7 +13942,7 @@
         <v>45587</v>
       </c>
       <c r="O97" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P97">
         <v>0.6153999999999999</v>
@@ -13889,7 +13950,7 @@
     </row>
     <row r="98" spans="1:16">
       <c r="A98" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B98">
         <v>9367017</v>
@@ -13898,13 +13959,13 @@
         <v>86</v>
       </c>
       <c r="D98" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E98" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F98" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G98">
         <v>99</v>
@@ -13931,7 +13992,7 @@
         <v>45588</v>
       </c>
       <c r="O98" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P98">
         <v>720.3</v>
@@ -13939,22 +14000,22 @@
     </row>
     <row r="99" spans="1:16">
       <c r="A99" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B99">
         <v>9367016</v>
       </c>
       <c r="C99" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D99" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E99" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F99" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G99">
         <v>38</v>
@@ -13981,7 +14042,7 @@
         <v>45588</v>
       </c>
       <c r="O99" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="P99">
         <v>1385</v>
@@ -13989,7 +14050,7 @@
     </row>
     <row r="100" spans="1:16">
       <c r="A100" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B100">
         <v>9562411</v>
@@ -13998,13 +14059,13 @@
         <v>86</v>
       </c>
       <c r="D100" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E100" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F100" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G100">
         <v>297</v>
@@ -14031,7 +14092,7 @@
         <v>45594</v>
       </c>
       <c r="O100" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P100">
         <v>756.2</v>
@@ -14039,22 +14100,22 @@
     </row>
     <row r="101" spans="1:16">
       <c r="A101" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B101">
         <v>9538338</v>
       </c>
       <c r="C101" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D101" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E101" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F101" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G101">
         <v>2</v>
@@ -14081,7 +14142,7 @@
         <v>45594</v>
       </c>
       <c r="O101" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P101">
         <v>9200</v>
@@ -14089,7 +14150,7 @@
     </row>
     <row r="102" spans="1:16">
       <c r="A102" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B102">
         <v>9538339</v>
@@ -14098,13 +14159,13 @@
         <v>88</v>
       </c>
       <c r="D102" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E102" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F102" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G102">
         <v>21</v>
@@ -14131,7 +14192,7 @@
         <v>45594</v>
       </c>
       <c r="O102" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P102">
         <v>3300</v>
@@ -14139,22 +14200,22 @@
     </row>
     <row r="103" spans="1:16">
       <c r="A103" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B103">
         <v>9538340</v>
       </c>
       <c r="C103" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D103" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E103" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F103" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G103">
         <v>2</v>
@@ -14181,7 +14242,7 @@
         <v>45594</v>
       </c>
       <c r="O103" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="P103">
         <v>18775</v>
@@ -14189,7 +14250,7 @@
     </row>
     <row r="104" spans="1:16">
       <c r="A104" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B104">
         <v>9538341</v>
@@ -14198,13 +14259,13 @@
         <v>95</v>
       </c>
       <c r="D104" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E104" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F104" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G104">
         <v>100</v>
@@ -14231,7 +14292,7 @@
         <v>45594</v>
       </c>
       <c r="O104" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="P104">
         <v>1033.1</v>
@@ -14239,7 +14300,7 @@
     </row>
     <row r="105" spans="1:16">
       <c r="A105" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B105">
         <v>9674949</v>
@@ -14248,13 +14309,13 @@
         <v>93</v>
       </c>
       <c r="D105" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E105" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F105" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G105">
         <v>4</v>
@@ -14289,7 +14350,7 @@
     </row>
     <row r="106" spans="1:16">
       <c r="A106" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B106">
         <v>9674950</v>
@@ -14298,13 +14359,13 @@
         <v>86</v>
       </c>
       <c r="D106" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E106" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F106" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G106">
         <v>186</v>
@@ -14331,7 +14392,7 @@
         <v>45597</v>
       </c>
       <c r="O106" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P106">
         <v>743.1</v>
@@ -14339,7 +14400,7 @@
     </row>
     <row r="107" spans="1:16">
       <c r="A107" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B107">
         <v>9672504</v>
@@ -14348,13 +14409,13 @@
         <v>82</v>
       </c>
       <c r="D107" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E107" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F107" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G107">
         <v>2</v>
@@ -14389,7 +14450,7 @@
     </row>
     <row r="108" spans="1:16">
       <c r="A108" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B108">
         <v>9672505</v>
@@ -14398,13 +14459,13 @@
         <v>97</v>
       </c>
       <c r="D108" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E108" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F108" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G108">
         <v>315</v>
@@ -14431,7 +14492,7 @@
         <v>45597</v>
       </c>
       <c r="O108" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P108">
         <v>320</v>
@@ -14439,22 +14500,22 @@
     </row>
     <row r="109" spans="1:16">
       <c r="A109" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B109">
         <v>9672506</v>
       </c>
       <c r="C109" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D109" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E109" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F109" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G109">
         <v>20</v>
@@ -14481,7 +14542,7 @@
         <v>45597</v>
       </c>
       <c r="O109" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P109">
         <v>1600</v>
@@ -14489,7 +14550,7 @@
     </row>
     <row r="110" spans="1:16">
       <c r="A110" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B110">
         <v>10313557</v>
@@ -14498,13 +14559,13 @@
         <v>86</v>
       </c>
       <c r="D110" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E110" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F110" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G110">
         <v>96</v>
@@ -14531,7 +14592,7 @@
         <v>45616</v>
       </c>
       <c r="O110" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P110">
         <v>765</v>
@@ -14539,22 +14600,22 @@
     </row>
     <row r="111" spans="1:16">
       <c r="A111" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B111">
         <v>10313556</v>
       </c>
       <c r="C111" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D111" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E111" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F111" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G111">
         <v>3</v>
@@ -14581,7 +14642,7 @@
         <v>45616</v>
       </c>
       <c r="O111" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P111">
         <v>24850</v>
@@ -14589,7 +14650,7 @@
     </row>
     <row r="112" spans="1:16">
       <c r="A112" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B112">
         <v>10359692</v>
@@ -14598,13 +14659,13 @@
         <v>86</v>
       </c>
       <c r="D112" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E112" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F112" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G112">
         <v>87</v>
@@ -14631,7 +14692,7 @@
         <v>45617</v>
       </c>
       <c r="O112" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P112">
         <v>764.5</v>
@@ -14639,7 +14700,7 @@
     </row>
     <row r="113" spans="1:16">
       <c r="A113" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B113">
         <v>10359691</v>
@@ -14648,13 +14709,13 @@
         <v>83</v>
       </c>
       <c r="D113" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E113" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F113" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G113">
         <v>10</v>
@@ -14689,7 +14750,7 @@
     </row>
     <row r="114" spans="1:16">
       <c r="A114" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B114">
         <v>10455319</v>
@@ -14698,7 +14759,7 @@
         <v>86</v>
       </c>
       <c r="D114" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E114" t="s">
         <v>160</v>
@@ -14731,7 +14792,7 @@
         <v>45621</v>
       </c>
       <c r="O114" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P114">
         <v>762.2</v>
@@ -14739,7 +14800,7 @@
     </row>
     <row r="115" spans="1:16">
       <c r="A115" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B115">
         <v>10560172</v>
@@ -14748,13 +14809,13 @@
         <v>86</v>
       </c>
       <c r="D115" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E115" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F115" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G115">
         <v>119</v>
@@ -14781,7 +14842,7 @@
         <v>45623</v>
       </c>
       <c r="O115" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P115">
         <v>763.5</v>
@@ -14789,22 +14850,22 @@
     </row>
     <row r="116" spans="1:16">
       <c r="A116" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B116">
         <v>10560171</v>
       </c>
       <c r="C116" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D116" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E116" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F116" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G116">
         <v>95</v>
@@ -14831,7 +14892,7 @@
         <v>45623</v>
       </c>
       <c r="O116" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P116">
         <v>973</v>
@@ -14839,7 +14900,7 @@
     </row>
     <row r="117" spans="1:16">
       <c r="A117" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B117">
         <v>10933763</v>
@@ -14848,13 +14909,13 @@
         <v>86</v>
       </c>
       <c r="D117" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E117" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F117" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G117">
         <v>155</v>
@@ -14881,7 +14942,7 @@
         <v>45632</v>
       </c>
       <c r="O117" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P117">
         <v>751.5</v>
@@ -14889,7 +14950,7 @@
     </row>
     <row r="118" spans="1:16">
       <c r="A118" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B118">
         <v>10933761</v>
@@ -14898,13 +14959,13 @@
         <v>93</v>
       </c>
       <c r="D118" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E118" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F118" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G118">
         <v>7</v>
@@ -14939,7 +15000,7 @@
     </row>
     <row r="119" spans="1:16">
       <c r="A119" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B119">
         <v>10933762</v>
@@ -14948,13 +15009,13 @@
         <v>94</v>
       </c>
       <c r="D119" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E119" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F119" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -14981,7 +15042,7 @@
         <v>45632</v>
       </c>
       <c r="O119" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="P119">
         <v>27775</v>
@@ -14989,22 +15050,22 @@
     </row>
     <row r="120" spans="1:16">
       <c r="A120" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B120">
         <v>10957376</v>
       </c>
       <c r="C120" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D120" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E120" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F120" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G120">
         <v>100</v>
@@ -15031,7 +15092,7 @@
         <v>45632</v>
       </c>
       <c r="O120" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="P120">
         <v>1030</v>
@@ -15039,7 +15100,7 @@
     </row>
     <row r="121" spans="1:16">
       <c r="A121" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B121">
         <v>11355097</v>
@@ -15048,13 +15109,13 @@
         <v>86</v>
       </c>
       <c r="D121" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E121" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F121" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G121">
         <v>299</v>
@@ -15081,7 +15142,7 @@
         <v>45644</v>
       </c>
       <c r="O121" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P121">
         <v>848.1862876254</v>
@@ -15089,7 +15150,7 @@
     </row>
     <row r="122" spans="1:16">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B122">
         <v>11355093</v>
@@ -15098,13 +15159,13 @@
         <v>87</v>
       </c>
       <c r="D122" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E122" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F122" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G122">
         <v>9</v>
@@ -15131,7 +15192,7 @@
         <v>45644</v>
       </c>
       <c r="O122" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P122">
         <v>6990</v>
@@ -15139,7 +15200,7 @@
     </row>
     <row r="123" spans="1:16">
       <c r="A123" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B123">
         <v>11355094</v>
@@ -15148,13 +15209,13 @@
         <v>92</v>
       </c>
       <c r="D123" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E123" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F123" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G123">
         <v>4</v>
@@ -15189,7 +15250,7 @@
     </row>
     <row r="124" spans="1:16">
       <c r="A124" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B124">
         <v>11355095</v>
@@ -15198,13 +15259,13 @@
         <v>90</v>
       </c>
       <c r="D124" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E124" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F124" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G124">
         <v>15</v>
@@ -15231,7 +15292,7 @@
         <v>45644</v>
       </c>
       <c r="O124" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P124">
         <v>3940</v>
@@ -15239,7 +15300,7 @@
     </row>
     <row r="125" spans="1:16">
       <c r="A125" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B125">
         <v>11355096</v>
@@ -15248,13 +15309,13 @@
         <v>83</v>
       </c>
       <c r="D125" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E125" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F125" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G125">
         <v>10</v>
@@ -15289,7 +15350,7 @@
     </row>
     <row r="126" spans="1:16">
       <c r="A126" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B126">
         <v>11615464</v>
@@ -15298,7 +15359,7 @@
         <v>91</v>
       </c>
       <c r="D126" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E126" t="s">
         <v>157</v>
@@ -15331,7 +15392,7 @@
         <v>45652</v>
       </c>
       <c r="O126" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P126">
         <v>14800</v>
@@ -15339,16 +15400,16 @@
     </row>
     <row r="127" spans="1:16">
       <c r="A127" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B127">
         <v>11615465</v>
       </c>
       <c r="C127" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D127" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E127" t="s">
         <v>157</v>
@@ -15381,7 +15442,7 @@
         <v>45652</v>
       </c>
       <c r="O127" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="P127">
         <v>27600</v>
@@ -15389,16 +15450,16 @@
     </row>
     <row r="128" spans="1:16">
       <c r="A128" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B128">
         <v>11615466</v>
       </c>
       <c r="C128" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D128" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E128" t="s">
         <v>157</v>
@@ -15431,7 +15492,7 @@
         <v>45652</v>
       </c>
       <c r="O128" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="P128">
         <v>1.021</v>
@@ -15439,7 +15500,7 @@
     </row>
     <row r="129" spans="1:16">
       <c r="A129" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B129">
         <v>328928</v>
@@ -15448,7 +15509,7 @@
         <v>86</v>
       </c>
       <c r="D129" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E129" t="s">
         <v>155</v>
@@ -15481,7 +15542,7 @@
         <v>45666</v>
       </c>
       <c r="O129" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P129">
         <v>799.4</v>
@@ -15489,7 +15550,7 @@
     </row>
     <row r="130" spans="1:16">
       <c r="A130" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B130">
         <v>328929</v>
@@ -15498,7 +15559,7 @@
         <v>86</v>
       </c>
       <c r="D130" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E130" t="s">
         <v>155</v>
@@ -15531,7 +15592,7 @@
         <v>45666</v>
       </c>
       <c r="O130" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P130">
         <v>0.6871</v>
@@ -15539,7 +15600,7 @@
     </row>
     <row r="131" spans="1:16">
       <c r="A131" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B131">
         <v>328930</v>
@@ -15548,7 +15609,7 @@
         <v>86</v>
       </c>
       <c r="D131" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E131" t="s">
         <v>155</v>
@@ -15581,7 +15642,7 @@
         <v>45666</v>
       </c>
       <c r="O131" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P131">
         <v>799.7</v>
@@ -15589,7 +15650,7 @@
     </row>
     <row r="132" spans="1:16">
       <c r="A132" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B132">
         <v>649634</v>
@@ -15598,7 +15659,7 @@
         <v>201</v>
       </c>
       <c r="D132" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E132" t="s">
         <v>153</v>
@@ -15639,7 +15700,7 @@
     </row>
     <row r="133" spans="1:16">
       <c r="A133" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B133">
         <v>753201</v>
@@ -15648,7 +15709,7 @@
         <v>86</v>
       </c>
       <c r="D133" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E133" t="s">
         <v>152</v>
@@ -15681,7 +15742,7 @@
         <v>45678</v>
       </c>
       <c r="O133" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P133">
         <v>0.6713</v>
@@ -15689,7 +15750,7 @@
     </row>
     <row r="134" spans="1:16">
       <c r="A134" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B134">
         <v>1570287</v>
@@ -15698,7 +15759,7 @@
         <v>86</v>
       </c>
       <c r="D134" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E134" t="s">
         <v>148</v>
@@ -15731,7 +15792,7 @@
         <v>45700</v>
       </c>
       <c r="O134" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P134">
         <v>771.3</v>
@@ -15739,7 +15800,7 @@
     </row>
     <row r="135" spans="1:16">
       <c r="A135" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B135">
         <v>2184640</v>
@@ -15748,7 +15809,7 @@
         <v>86</v>
       </c>
       <c r="D135" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E135" t="s">
         <v>147</v>
@@ -15781,7 +15842,7 @@
         <v>45721</v>
       </c>
       <c r="O135" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P135">
         <v>805.6</v>
@@ -15789,7 +15850,7 @@
     </row>
     <row r="136" spans="1:16">
       <c r="A136" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B136">
         <v>2743786</v>
@@ -15798,7 +15859,7 @@
         <v>86</v>
       </c>
       <c r="D136" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E136" t="s">
         <v>146</v>
@@ -15831,7 +15892,7 @@
         <v>45736</v>
       </c>
       <c r="O136" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P136">
         <v>820.9</v>
@@ -15839,7 +15900,7 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B137">
         <v>2920435</v>
@@ -15848,7 +15909,7 @@
         <v>86</v>
       </c>
       <c r="D137" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E137" t="s">
         <v>145</v>
@@ -15881,7 +15942,7 @@
         <v>45743</v>
       </c>
       <c r="O137" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P137">
         <v>834.8</v>
@@ -15889,7 +15950,7 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B138">
         <v>3198439</v>
@@ -15898,7 +15959,7 @@
         <v>86</v>
       </c>
       <c r="D138" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E138" t="s">
         <v>144</v>
@@ -15931,7 +15992,7 @@
         <v>45751</v>
       </c>
       <c r="O138" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P138">
         <v>825.3</v>
@@ -15939,22 +16000,22 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B139">
         <v>3333331</v>
       </c>
       <c r="C139" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D139" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E139" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F139" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G139">
         <v>83</v>
@@ -15989,7 +16050,7 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B140">
         <v>3333332</v>
@@ -15998,13 +16059,13 @@
         <v>87</v>
       </c>
       <c r="D140" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E140" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F140" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G140">
         <v>15</v>
@@ -16031,7 +16092,7 @@
         <v>45755</v>
       </c>
       <c r="O140" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P140">
         <v>6193.3333333333</v>
@@ -16039,7 +16100,7 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B141">
         <v>3333333</v>
@@ -16048,13 +16109,13 @@
         <v>82</v>
       </c>
       <c r="D141" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E141" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F141" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G141">
         <v>12</v>
@@ -16089,7 +16150,7 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B142">
         <v>3368832</v>
@@ -16098,13 +16159,13 @@
         <v>88</v>
       </c>
       <c r="D142" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E142" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F142" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G142">
         <v>33</v>
@@ -16131,7 +16192,7 @@
         <v>45755</v>
       </c>
       <c r="O142" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P142">
         <v>2946.6666666666</v>
@@ -16139,7 +16200,7 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B143">
         <v>3532874</v>
@@ -16148,13 +16209,13 @@
         <v>86</v>
       </c>
       <c r="D143" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E143" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F143" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G143">
         <v>320</v>
@@ -16181,7 +16242,7 @@
         <v>45761</v>
       </c>
       <c r="O143" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P143">
         <v>801.2</v>
@@ -16189,7 +16250,7 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B144">
         <v>3532873</v>
@@ -16198,13 +16259,13 @@
         <v>82</v>
       </c>
       <c r="D144" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E144" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F144" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G144">
         <v>6</v>
@@ -16239,7 +16300,7 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B145">
         <v>3532875</v>
@@ -16248,13 +16309,13 @@
         <v>86</v>
       </c>
       <c r="D145" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E145" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F145" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G145">
         <v>320</v>
@@ -16281,7 +16342,7 @@
         <v>45761</v>
       </c>
       <c r="O145" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P145">
         <v>0.6567</v>
@@ -16289,7 +16350,7 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B146">
         <v>3591042</v>
@@ -16298,7 +16359,7 @@
         <v>86</v>
       </c>
       <c r="D146" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E146" t="s">
         <v>143</v>
@@ -16331,7 +16392,7 @@
         <v>45762</v>
       </c>
       <c r="O146" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P146">
         <v>0.6585</v>
@@ -16339,7 +16400,7 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B147">
         <v>3867747</v>
@@ -16348,13 +16409,13 @@
         <v>82</v>
       </c>
       <c r="D147" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E147" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F147" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G147">
         <v>25</v>
@@ -16389,7 +16450,7 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B148">
         <v>3867748</v>
@@ -16398,13 +16459,13 @@
         <v>89</v>
       </c>
       <c r="D148" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E148" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F148" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G148">
         <v>1359</v>
@@ -16431,7 +16492,7 @@
         <v>45772</v>
       </c>
       <c r="O148" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P148">
         <v>17.745</v>
@@ -16439,7 +16500,7 @@
     </row>
     <row r="149" spans="1:16">
       <c r="A149" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B149">
         <v>5072207</v>
@@ -16448,13 +16509,13 @@
         <v>89</v>
       </c>
       <c r="D149" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E149" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F149" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G149">
         <v>1032</v>
@@ -16481,7 +16542,7 @@
         <v>45817</v>
       </c>
       <c r="O149" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P149">
         <v>15.895</v>
@@ -16489,16 +16550,16 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B150">
         <v>6004728</v>
       </c>
       <c r="C150" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D150" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E150" t="s">
         <v>137</v>
@@ -16539,16 +16600,16 @@
     </row>
     <row r="151" spans="1:16">
       <c r="A151" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B151">
         <v>6004729</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D151" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E151" t="s">
         <v>137</v>
@@ -16589,7 +16650,7 @@
     </row>
     <row r="152" spans="1:16">
       <c r="A152" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B152">
         <v>6069007</v>
@@ -16598,7 +16659,7 @@
         <v>86</v>
       </c>
       <c r="D152" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E152" t="s">
         <v>135</v>
@@ -16631,7 +16692,7 @@
         <v>45852</v>
       </c>
       <c r="O152" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P152">
         <v>768.2</v>
@@ -16639,16 +16700,16 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B153">
         <v>6069005</v>
       </c>
       <c r="C153" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D153" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E153" t="s">
         <v>135</v>
@@ -16689,7 +16750,7 @@
     </row>
     <row r="154" spans="1:16">
       <c r="A154" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B154">
         <v>6069006</v>
@@ -16698,7 +16759,7 @@
         <v>82</v>
       </c>
       <c r="D154" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E154" t="s">
         <v>135</v>
@@ -16739,7 +16800,7 @@
     </row>
     <row r="155" spans="1:16">
       <c r="A155" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B155">
         <v>6167854</v>
@@ -16748,7 +16809,7 @@
         <v>86</v>
       </c>
       <c r="D155" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E155" t="s">
         <v>134</v>
@@ -16781,7 +16842,7 @@
         <v>45854</v>
       </c>
       <c r="O155" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P155">
         <v>756.1</v>
@@ -16789,7 +16850,7 @@
     </row>
     <row r="156" spans="1:16">
       <c r="A156" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B156">
         <v>6367001</v>
@@ -16798,13 +16859,13 @@
         <v>87</v>
       </c>
       <c r="D156" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E156" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F156" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G156">
         <v>55</v>
@@ -16831,7 +16892,7 @@
         <v>45860</v>
       </c>
       <c r="O156" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P156">
         <v>6390</v>
@@ -16839,7 +16900,7 @@
     </row>
     <row r="157" spans="1:16">
       <c r="A157" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B157">
         <v>6367002</v>
@@ -16848,13 +16909,13 @@
         <v>88</v>
       </c>
       <c r="D157" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E157" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F157" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G157">
         <v>121</v>
@@ -16881,7 +16942,7 @@
         <v>45860</v>
       </c>
       <c r="O157" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P157">
         <v>2835</v>
@@ -16889,7 +16950,7 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B158">
         <v>6367003</v>
@@ -16898,13 +16959,13 @@
         <v>86</v>
       </c>
       <c r="D158" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E158" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F158" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G158">
         <v>1984</v>
@@ -16931,7 +16992,7 @@
         <v>45860</v>
       </c>
       <c r="O158" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P158">
         <v>742.9</v>
@@ -16939,7 +17000,7 @@
     </row>
     <row r="159" spans="1:16">
       <c r="A159" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B159">
         <v>6367004</v>
@@ -16948,13 +17009,13 @@
         <v>89</v>
       </c>
       <c r="D159" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E159" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F159" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G159">
         <v>235</v>
@@ -16981,7 +17042,7 @@
         <v>45860</v>
       </c>
       <c r="O159" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P159">
         <v>15.425</v>
@@ -16989,7 +17050,7 @@
     </row>
     <row r="160" spans="1:16">
       <c r="A160" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B160">
         <v>6478375</v>
@@ -16998,7 +17059,7 @@
         <v>88</v>
       </c>
       <c r="D160" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E160" t="s">
         <v>133</v>
@@ -17031,7 +17092,7 @@
         <v>45862</v>
       </c>
       <c r="O160" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P160">
         <v>2990</v>
@@ -17039,7 +17100,7 @@
     </row>
     <row r="161" spans="1:16">
       <c r="A161" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B161">
         <v>6589037</v>
@@ -17048,13 +17109,13 @@
         <v>83</v>
       </c>
       <c r="D161" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E161" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F161" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G161">
         <v>14</v>
@@ -17089,7 +17150,7 @@
     </row>
     <row r="162" spans="1:16">
       <c r="A162" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B162">
         <v>6589035</v>
@@ -17098,13 +17159,13 @@
         <v>82</v>
       </c>
       <c r="D162" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E162" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F162" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G162">
         <v>3</v>
@@ -17139,7 +17200,7 @@
     </row>
     <row r="163" spans="1:16">
       <c r="A163" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B163">
         <v>6589036</v>
@@ -17148,13 +17209,13 @@
         <v>88</v>
       </c>
       <c r="D163" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E163" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F163" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G163">
         <v>28</v>
@@ -17181,7 +17242,7 @@
         <v>45866</v>
       </c>
       <c r="O163" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P163">
         <v>3415</v>
@@ -17189,7 +17250,7 @@
     </row>
     <row r="164" spans="1:16">
       <c r="A164" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B164">
         <v>6634259</v>
@@ -17198,13 +17259,13 @@
         <v>83</v>
       </c>
       <c r="D164" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E164" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F164" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G164">
         <v>9</v>
@@ -17239,7 +17300,7 @@
     </row>
     <row r="165" spans="1:16">
       <c r="A165" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B165">
         <v>6699255</v>
@@ -17248,13 +17309,13 @@
         <v>87</v>
       </c>
       <c r="D165" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E165" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F165" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G165">
         <v>37</v>
@@ -17281,7 +17342,7 @@
         <v>45868</v>
       </c>
       <c r="O165" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P165">
         <v>7650</v>
@@ -17289,7 +17350,7 @@
     </row>
     <row r="166" spans="1:16">
       <c r="A166" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B166">
         <v>6699256</v>
@@ -17298,13 +17359,13 @@
         <v>88</v>
       </c>
       <c r="D166" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E166" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F166" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G166">
         <v>115</v>
@@ -17331,7 +17392,7 @@
         <v>45868</v>
       </c>
       <c r="O166" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P166">
         <v>3390</v>
@@ -17339,7 +17400,7 @@
     </row>
     <row r="167" spans="1:16">
       <c r="A167" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B167">
         <v>6699257</v>
@@ -17348,13 +17409,13 @@
         <v>88</v>
       </c>
       <c r="D167" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E167" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F167" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G167">
         <v>58</v>
@@ -17381,7 +17442,7 @@
         <v>45868</v>
       </c>
       <c r="O167" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P167">
         <v>3385</v>
@@ -17389,7 +17450,7 @@
     </row>
     <row r="168" spans="1:16">
       <c r="A168" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B168">
         <v>6699258</v>
@@ -17398,13 +17459,13 @@
         <v>86</v>
       </c>
       <c r="D168" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E168" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F168" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G168">
         <v>620</v>
@@ -17431,7 +17492,7 @@
         <v>45868</v>
       </c>
       <c r="O168" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P168">
         <v>792.5</v>
@@ -17439,7 +17500,7 @@
     </row>
     <row r="169" spans="1:16">
       <c r="A169" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B169">
         <v>6888334</v>
@@ -17448,13 +17509,13 @@
         <v>84</v>
       </c>
       <c r="D169" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E169" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F169" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G169">
         <v>225</v>
@@ -17481,7 +17542,7 @@
         <v>45873</v>
       </c>
       <c r="O169" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P169">
         <v>6710</v>
@@ -17489,7 +17550,7 @@
     </row>
     <row r="170" spans="1:16">
       <c r="A170" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B170">
         <v>6888335</v>
@@ -17498,13 +17559,13 @@
         <v>86</v>
       </c>
       <c r="D170" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E170" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F170" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G170">
         <v>1848</v>
@@ -17531,7 +17592,7 @@
         <v>45873</v>
       </c>
       <c r="O170" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P170">
         <v>811.7</v>
@@ -17539,7 +17600,7 @@
     </row>
     <row r="171" spans="1:16">
       <c r="A171" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B171">
         <v>6888336</v>
@@ -17548,13 +17609,13 @@
         <v>89</v>
       </c>
       <c r="D171" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E171" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F171" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G171">
         <v>2626</v>
@@ -17581,7 +17642,7 @@
         <v>45873</v>
       </c>
       <c r="O171" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P171">
         <v>16</v>
@@ -17589,7 +17650,7 @@
     </row>
     <row r="172" spans="1:16">
       <c r="A172" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B172">
         <v>6943451</v>
@@ -17598,13 +17659,13 @@
         <v>83</v>
       </c>
       <c r="D172" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E172" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F172" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G172">
         <v>19</v>
@@ -17639,7 +17700,7 @@
     </row>
     <row r="173" spans="1:16">
       <c r="A173" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B173">
         <v>6943450</v>
@@ -17648,13 +17709,13 @@
         <v>82</v>
       </c>
       <c r="D173" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E173" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F173" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G173">
         <v>4</v>
@@ -17689,7 +17750,7 @@
     </row>
     <row r="174" spans="1:16">
       <c r="A174" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B174">
         <v>7236559</v>
@@ -17698,7 +17759,7 @@
         <v>83</v>
       </c>
       <c r="D174" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E174" t="s">
         <v>132</v>
@@ -17739,7 +17800,7 @@
     </row>
     <row r="175" spans="1:16">
       <c r="A175" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B175">
         <v>7236558</v>
@@ -17748,7 +17809,7 @@
         <v>82</v>
       </c>
       <c r="D175" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E175" t="s">
         <v>132</v>
@@ -17789,7 +17850,7 @@
     </row>
     <row r="176" spans="1:16">
       <c r="A176" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B176">
         <v>7429752</v>
@@ -17798,7 +17859,7 @@
         <v>83</v>
       </c>
       <c r="D176" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E176" t="s">
         <v>131</v>
@@ -17839,7 +17900,7 @@
     </row>
     <row r="177" spans="1:16">
       <c r="A177" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B177">
         <v>7737108</v>
@@ -17848,13 +17909,13 @@
         <v>83</v>
       </c>
       <c r="D177" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E177" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F177" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G177">
         <v>413</v>
@@ -17889,7 +17950,7 @@
     </row>
     <row r="178" spans="1:16">
       <c r="A178" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B178">
         <v>7737105</v>
@@ -17898,13 +17959,13 @@
         <v>84</v>
       </c>
       <c r="D178" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E178" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F178" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G178">
         <v>225</v>
@@ -17931,7 +17992,7 @@
         <v>45894</v>
       </c>
       <c r="O178" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P178">
         <v>5890</v>
@@ -17939,7 +18000,7 @@
     </row>
     <row r="179" spans="1:16">
       <c r="A179" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B179">
         <v>7737106</v>
@@ -17948,13 +18009,13 @@
         <v>87</v>
       </c>
       <c r="D179" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E179" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F179" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G179">
         <v>107</v>
@@ -17981,7 +18042,7 @@
         <v>45894</v>
       </c>
       <c r="O179" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P179">
         <v>7330</v>
@@ -17989,7 +18050,7 @@
     </row>
     <row r="180" spans="1:16">
       <c r="A180" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B180">
         <v>7737107</v>
@@ -17998,13 +18059,13 @@
         <v>88</v>
       </c>
       <c r="D180" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E180" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F180" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G180">
         <v>153</v>
@@ -18031,7 +18092,7 @@
         <v>45894</v>
       </c>
       <c r="O180" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P180">
         <v>3355</v>
@@ -18039,7 +18100,7 @@
     </row>
     <row r="181" spans="1:16">
       <c r="A181" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B181">
         <v>7737109</v>
@@ -18048,13 +18109,13 @@
         <v>86</v>
       </c>
       <c r="D181" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E181" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F181" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G181">
         <v>3447</v>
@@ -18081,7 +18142,7 @@
         <v>45894</v>
       </c>
       <c r="O181" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P181">
         <v>788</v>
@@ -18089,22 +18150,22 @@
     </row>
     <row r="182" spans="1:16">
       <c r="A182" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B182">
         <v>8408803</v>
       </c>
       <c r="C182" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D182" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E182" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F182" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G182">
         <v>103</v>
@@ -18131,7 +18192,7 @@
         <v>45908</v>
       </c>
       <c r="O182" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="P182">
         <v>4735</v>
@@ -18139,7 +18200,7 @@
     </row>
     <row r="183" spans="1:16">
       <c r="A183" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B183">
         <v>8408804</v>
@@ -18148,13 +18209,13 @@
         <v>84</v>
       </c>
       <c r="D183" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E183" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F183" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G183">
         <v>47</v>
@@ -18181,7 +18242,7 @@
         <v>45908</v>
       </c>
       <c r="O183" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P183">
         <v>4780</v>
@@ -18189,7 +18250,7 @@
     </row>
     <row r="184" spans="1:16">
       <c r="A184" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B184">
         <v>8408805</v>
@@ -18198,13 +18259,13 @@
         <v>82</v>
       </c>
       <c r="D184" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E184" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F184" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G184">
         <v>24</v>
@@ -18239,7 +18300,7 @@
     </row>
     <row r="185" spans="1:16">
       <c r="A185" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B185">
         <v>8492244</v>
@@ -18248,7 +18309,7 @@
         <v>93</v>
       </c>
       <c r="D185" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E185" t="s">
         <v>129</v>
@@ -18289,7 +18350,7 @@
     </row>
     <row r="186" spans="1:16">
       <c r="A186" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B186">
         <v>8492245</v>
@@ -18298,7 +18359,7 @@
         <v>83</v>
       </c>
       <c r="D186" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E186" t="s">
         <v>129</v>
@@ -18339,7 +18400,7 @@
     </row>
     <row r="187" spans="1:16">
       <c r="A187" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B187">
         <v>8916688</v>
@@ -18348,13 +18409,13 @@
         <v>84</v>
       </c>
       <c r="D187" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E187" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G187">
         <v>5</v>
@@ -18381,7 +18442,7 @@
         <v>45918</v>
       </c>
       <c r="O187" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P187">
         <v>3995</v>
@@ -18389,7 +18450,7 @@
     </row>
     <row r="188" spans="1:16">
       <c r="A188" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B188">
         <v>8916689</v>
@@ -18398,13 +18459,13 @@
         <v>82</v>
       </c>
       <c r="D188" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E188" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G188">
         <v>2</v>
@@ -18439,7 +18500,7 @@
     </row>
     <row r="189" spans="1:16">
       <c r="A189" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B189">
         <v>8909679</v>
@@ -18448,13 +18509,13 @@
         <v>93</v>
       </c>
       <c r="D189" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E189" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G189">
         <v>5</v>
@@ -18489,7 +18550,7 @@
     </row>
     <row r="190" spans="1:16">
       <c r="A190" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B190">
         <v>9058877</v>
@@ -18498,7 +18559,7 @@
         <v>83</v>
       </c>
       <c r="D190" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E190" t="s">
         <v>187</v>
@@ -18539,16 +18600,16 @@
     </row>
     <row r="191" spans="1:16">
       <c r="A191" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B191">
         <v>9058874</v>
       </c>
       <c r="C191" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D191" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E191" t="s">
         <v>187</v>
@@ -18581,7 +18642,7 @@
         <v>45922</v>
       </c>
       <c r="O191" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="P191">
         <v>4732.5</v>
@@ -18589,7 +18650,7 @@
     </row>
     <row r="192" spans="1:16">
       <c r="A192" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B192">
         <v>9058875</v>
@@ -18598,7 +18659,7 @@
         <v>84</v>
       </c>
       <c r="D192" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E192" t="s">
         <v>187</v>
@@ -18631,7 +18692,7 @@
         <v>45922</v>
       </c>
       <c r="O192" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P192">
         <v>4577.5</v>
@@ -18639,7 +18700,7 @@
     </row>
     <row r="193" spans="1:16">
       <c r="A193" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B193">
         <v>9058876</v>
@@ -18648,7 +18709,7 @@
         <v>82</v>
       </c>
       <c r="D193" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E193" t="s">
         <v>187</v>
@@ -18689,16 +18750,16 @@
     </row>
     <row r="194" spans="1:16">
       <c r="A194" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B194">
         <v>9060004</v>
       </c>
       <c r="C194" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D194" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E194" t="s">
         <v>187</v>
@@ -18731,7 +18792,7 @@
         <v>45922</v>
       </c>
       <c r="O194" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="P194">
         <v>4722.5</v>
@@ -18739,7 +18800,7 @@
     </row>
     <row r="195" spans="1:16">
       <c r="A195" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B195">
         <v>9176501</v>
@@ -18748,7 +18809,7 @@
         <v>83</v>
       </c>
       <c r="D195" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E195" t="s">
         <v>127</v>
@@ -18789,7 +18850,7 @@
     </row>
     <row r="196" spans="1:16">
       <c r="A196" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B196">
         <v>10233181</v>
@@ -18798,7 +18859,7 @@
         <v>87</v>
       </c>
       <c r="D196" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E196" t="s">
         <v>125</v>
@@ -18831,7 +18892,7 @@
         <v>45950</v>
       </c>
       <c r="O196" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P196">
         <v>6625</v>
@@ -18839,7 +18900,7 @@
     </row>
     <row r="197" spans="1:16">
       <c r="A197" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B197">
         <v>10343811</v>
@@ -18848,13 +18909,13 @@
         <v>87</v>
       </c>
       <c r="D197" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E197" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F197" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G197">
         <v>7</v>
@@ -18881,7 +18942,7 @@
         <v>45952</v>
       </c>
       <c r="O197" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P197">
         <v>6915</v>
@@ -18889,7 +18950,7 @@
     </row>
     <row r="198" spans="1:16">
       <c r="A198" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B198">
         <v>10971976</v>
@@ -18898,13 +18959,13 @@
         <v>83</v>
       </c>
       <c r="D198" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E198" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F198" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G198">
         <v>7</v>
@@ -18939,7 +19000,7 @@
     </row>
     <row r="199" spans="1:16">
       <c r="A199" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B199">
         <v>2923909</v>
@@ -18948,13 +19009,13 @@
         <v>83</v>
       </c>
       <c r="D199" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E199" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F199" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G199">
         <v>90</v>
@@ -18989,7 +19050,7 @@
     </row>
     <row r="200" spans="1:16">
       <c r="A200" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B200">
         <v>3267919</v>
@@ -18998,13 +19059,13 @@
         <v>82</v>
       </c>
       <c r="D200" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E200" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F200" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G200">
         <v>7</v>
@@ -19039,7 +19100,7 @@
     </row>
     <row r="201" spans="1:16">
       <c r="A201" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B201">
         <v>3267920</v>
@@ -19048,13 +19109,13 @@
         <v>83</v>
       </c>
       <c r="D201" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E201" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F201" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G201">
         <v>99</v>
@@ -19089,7 +19150,7 @@
     </row>
     <row r="202" spans="1:16">
       <c r="A202" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B202">
         <v>3285058</v>
@@ -19098,13 +19159,13 @@
         <v>83</v>
       </c>
       <c r="D202" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E202" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F202" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G202">
         <v>90</v>
@@ -19139,7 +19200,7 @@
     </row>
     <row r="203" spans="1:16">
       <c r="A203" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B203">
         <v>4018683</v>
@@ -19148,13 +19209,13 @@
         <v>83</v>
       </c>
       <c r="D203" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E203" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F203" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G203">
         <v>338</v>
@@ -19189,22 +19250,22 @@
     </row>
     <row r="204" spans="1:16">
       <c r="A204" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B204">
         <v>4656488</v>
       </c>
       <c r="C204" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D204" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E204" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F204" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G204">
         <v>818</v>
@@ -19231,7 +19292,7 @@
         <v>46140</v>
       </c>
       <c r="O204" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P204">
         <v>3851.0819070904</v>
@@ -19239,7 +19300,7 @@
     </row>
     <row r="205" spans="1:16">
       <c r="A205" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B205">
         <v>6147294</v>
@@ -19248,7 +19309,7 @@
         <v>83</v>
       </c>
       <c r="D205" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E205" t="s">
         <v>115</v>
@@ -19289,7 +19350,7 @@
     </row>
     <row r="206" spans="1:16">
       <c r="A206" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B206">
         <v>6339517</v>
@@ -19298,13 +19359,13 @@
         <v>86</v>
       </c>
       <c r="D206" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E206" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F206" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G206">
         <v>879</v>
@@ -19331,7 +19392,7 @@
         <v>46182</v>
       </c>
       <c r="O206" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P206">
         <v>0.6417</v>
@@ -19339,7 +19400,7 @@
     </row>
     <row r="207" spans="1:16">
       <c r="A207" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B207">
         <v>6339516</v>
@@ -19348,13 +19409,13 @@
         <v>83</v>
       </c>
       <c r="D207" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E207" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F207" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G207">
         <v>146</v>
@@ -19389,7 +19450,7 @@
     </row>
     <row r="208" spans="1:16">
       <c r="A208" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B208">
         <v>6339518</v>
@@ -19398,13 +19459,13 @@
         <v>86</v>
       </c>
       <c r="D208" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E208" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F208" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G208">
         <v>879</v>
@@ -19431,7 +19492,7 @@
         <v>46182</v>
       </c>
       <c r="O208" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P208">
         <v>938.7</v>
@@ -19439,22 +19500,22 @@
     </row>
     <row r="209" spans="1:16">
       <c r="A209" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B209">
         <v>6446442</v>
       </c>
       <c r="C209" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D209" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E209" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F209" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G209">
         <v>540</v>
@@ -19481,7 +19542,7 @@
         <v>46184</v>
       </c>
       <c r="O209" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P209">
         <v>3990</v>
@@ -19489,7 +19550,7 @@
     </row>
     <row r="210" spans="1:16">
       <c r="A210" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B210">
         <v>6864642</v>
@@ -19498,13 +19559,13 @@
         <v>84</v>
       </c>
       <c r="D210" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E210" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F210" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G210">
         <v>129</v>
@@ -19531,7 +19592,7 @@
         <v>46197</v>
       </c>
       <c r="O210" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P210">
         <v>7700</v>
@@ -19539,7 +19600,7 @@
     </row>
     <row r="211" spans="1:16">
       <c r="A211" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B211">
         <v>6864643</v>
@@ -19548,13 +19609,13 @@
         <v>82</v>
       </c>
       <c r="D211" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E211" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F211" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G211">
         <v>13</v>
@@ -19589,7 +19650,7 @@
     </row>
     <row r="212" spans="1:16">
       <c r="A212" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B212">
         <v>7035923</v>
@@ -19598,7 +19659,7 @@
         <v>84</v>
       </c>
       <c r="D212" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E212" t="s">
         <v>112</v>
@@ -19631,7 +19692,7 @@
         <v>46202</v>
       </c>
       <c r="O212" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P212">
         <v>8000</v>
@@ -19639,7 +19700,7 @@
     </row>
     <row r="213" spans="1:16">
       <c r="A213" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B213">
         <v>7154878</v>
@@ -19648,13 +19709,13 @@
         <v>84</v>
       </c>
       <c r="D213" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E213" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F213" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G213">
         <v>64</v>
@@ -19681,7 +19742,7 @@
         <v>46204</v>
       </c>
       <c r="O213" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P213">
         <v>7700</v>
@@ -19689,7 +19750,7 @@
     </row>
     <row r="214" spans="1:16">
       <c r="A214" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B214">
         <v>9028136</v>
@@ -19698,13 +19759,13 @@
         <v>84</v>
       </c>
       <c r="D214" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E214" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F214" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G214">
         <v>503</v>
@@ -19731,7 +19792,7 @@
         <v>46248</v>
       </c>
       <c r="O214" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P214">
         <v>7080</v>
@@ -19739,7 +19800,7 @@
     </row>
     <row r="215" spans="1:16">
       <c r="A215" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B215">
         <v>9298842</v>
@@ -19748,13 +19809,13 @@
         <v>84</v>
       </c>
       <c r="D215" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E215" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F215" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G215">
         <v>503</v>
@@ -19781,7 +19842,7 @@
         <v>46255</v>
       </c>
       <c r="O215" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P215">
         <v>6609.9005964214</v>
@@ -19789,22 +19850,22 @@
     </row>
     <row r="216" spans="1:16">
       <c r="A216" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B216">
         <v>9298843</v>
       </c>
       <c r="C216" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D216" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E216" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F216" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G216">
         <v>278</v>
@@ -19831,7 +19892,7 @@
         <v>46255</v>
       </c>
       <c r="O216" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P216">
         <v>3330</v>
@@ -19839,7 +19900,7 @@
     </row>
     <row r="217" spans="1:16">
       <c r="A217" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B217">
         <v>10350610</v>
@@ -19848,7 +19909,7 @@
         <v>83</v>
       </c>
       <c r="D217" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E217" t="s">
         <v>103</v>
@@ -19889,7 +19950,7 @@
     </row>
     <row r="218" spans="1:16">
       <c r="A218" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B218">
         <v>10443261</v>
@@ -19898,13 +19959,13 @@
         <v>82</v>
       </c>
       <c r="D218" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E218" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F218" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G218">
         <v>100</v>
@@ -19939,7 +20000,7 @@
     </row>
     <row r="219" spans="1:16">
       <c r="A219" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B219">
         <v>10583557</v>
@@ -19948,13 +20009,13 @@
         <v>201</v>
       </c>
       <c r="D219" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E219" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F219" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G219">
         <v>42</v>
@@ -19989,7 +20050,7 @@
     </row>
     <row r="220" spans="1:16">
       <c r="A220" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B220">
         <v>10668132</v>
@@ -19998,13 +20059,13 @@
         <v>82</v>
       </c>
       <c r="D220" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E220" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F220" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G220">
         <v>232</v>
@@ -20039,7 +20100,7 @@
     </row>
     <row r="221" spans="1:16">
       <c r="A221" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B221">
         <v>10641020</v>
@@ -20048,13 +20109,13 @@
         <v>83</v>
       </c>
       <c r="D221" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E221" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F221" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G221">
         <v>139</v>
@@ -20089,22 +20150,22 @@
     </row>
     <row r="222" spans="1:16">
       <c r="A222" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B222">
         <v>10845350</v>
       </c>
       <c r="C222" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="D222" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E222" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F222" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G222">
         <v>195</v>
@@ -20149,15 +20210,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B2">
         <v>1110511.68</v>
@@ -20165,7 +20226,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B3">
         <v>1292494.146087911</v>
@@ -20173,10 +20234,10 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B4">
-        <v>1167749.330769231</v>
+        <v>1160634.330769231</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="364">
   <si>
     <t>Descripcion</t>
   </si>
@@ -1054,6 +1054,9 @@
     <t>2026-09-24</t>
   </si>
   <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
     <t>2024-04-11</t>
   </si>
   <si>
@@ -1097,6 +1100,9 @@
   </si>
   <si>
     <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
   </si>
   <si>
     <t>Flujo Fondeo Neto</t>
@@ -4499,13 +4505,13 @@
         <v>190</v>
       </c>
       <c r="F2">
-        <v>5065</v>
+        <v>4992.5</v>
       </c>
       <c r="G2">
-        <v>987675</v>
+        <v>973537.5</v>
       </c>
       <c r="H2">
-        <v>-15406.37</v>
+        <v>-29543.87</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4513,25 +4519,25 @@
         <v>82</v>
       </c>
       <c r="B3">
-        <v>332</v>
+        <v>393</v>
       </c>
       <c r="C3">
-        <v>8192.675810936051</v>
+        <v>8188.220532393815</v>
       </c>
       <c r="D3">
-        <v>2719968.369230769</v>
+        <v>3217970.669230769</v>
       </c>
       <c r="E3" t="s">
         <v>190</v>
       </c>
       <c r="F3">
-        <v>8455</v>
+        <v>8145</v>
       </c>
       <c r="G3">
-        <v>2807060</v>
+        <v>3200985</v>
       </c>
       <c r="H3">
-        <v>87091.63076923089</v>
+        <v>-16985.66923076939</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4551,13 +4557,13 @@
         <v>190</v>
       </c>
       <c r="F4">
-        <v>23670</v>
+        <v>23280</v>
       </c>
       <c r="G4">
-        <v>994140</v>
+        <v>977760</v>
       </c>
       <c r="H4">
-        <v>-21562.60999999999</v>
+        <v>-37942.60999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4565,13 +4571,13 @@
         <v>202</v>
       </c>
       <c r="B5">
-        <v>1110511.68</v>
+        <v>612509.38</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1110511.68</v>
+        <v>612509.38</v>
       </c>
       <c r="E5" t="s">
         <v>190</v>
@@ -4580,7 +4586,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1110511.68</v>
+        <v>612509.38</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -8841,7 +8847,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8950,27 +8956,53 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46294</v>
+      </c>
+      <c r="C5">
+        <v>61</v>
+      </c>
+      <c r="D5">
+        <v>8110</v>
+      </c>
+      <c r="E5">
+        <v>53.97213114754049</v>
+      </c>
+      <c r="F5">
+        <v>8163.97213114754</v>
+      </c>
+      <c r="G5">
+        <v>8218.667445230401</v>
+      </c>
+      <c r="H5">
+        <v>498002.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="1">
         <v>46283</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>42</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>23880</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>303.3954761904752</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>24183.39547619048</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>24494.59944022999</v>
       </c>
-      <c r="H5">
+      <c r="H6">
         <v>1015702.61</v>
       </c>
     </row>
@@ -8997,7 +9029,7 @@
         <v>245</v>
       </c>
       <c r="B2">
-        <v>567710.775</v>
+        <v>570703.775</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9005,7 +9037,7 @@
         <v>246</v>
       </c>
       <c r="B3">
-        <v>46487.3</v>
+        <v>46786.60000000001</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9013,7 +9045,7 @@
         <v>247</v>
       </c>
       <c r="B4">
-        <v>614198.0750000001</v>
+        <v>617490.375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9095,7 +9127,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P222"/>
+  <dimension ref="A1:P223"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -9765,7 +9797,7 @@
         <v>290</v>
       </c>
       <c r="F14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G14">
         <v>26</v>
@@ -9815,7 +9847,7 @@
         <v>290</v>
       </c>
       <c r="F15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -9865,7 +9897,7 @@
         <v>290</v>
       </c>
       <c r="F16" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -9915,7 +9947,7 @@
         <v>290</v>
       </c>
       <c r="F17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -9965,7 +9997,7 @@
         <v>291</v>
       </c>
       <c r="F18" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G18">
         <v>55</v>
@@ -10015,7 +10047,7 @@
         <v>292</v>
       </c>
       <c r="F19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -10065,7 +10097,7 @@
         <v>292</v>
       </c>
       <c r="F20" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -10115,7 +10147,7 @@
         <v>292</v>
       </c>
       <c r="F21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -10165,7 +10197,7 @@
         <v>292</v>
       </c>
       <c r="F22" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -10215,7 +10247,7 @@
         <v>292</v>
       </c>
       <c r="F23" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -10265,7 +10297,7 @@
         <v>292</v>
       </c>
       <c r="F24" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G24">
         <v>4</v>
@@ -10315,7 +10347,7 @@
         <v>292</v>
       </c>
       <c r="F25" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -10365,7 +10397,7 @@
         <v>293</v>
       </c>
       <c r="F26" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G26">
         <v>9</v>
@@ -10415,7 +10447,7 @@
         <v>293</v>
       </c>
       <c r="F27" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G27">
         <v>6</v>
@@ -10465,7 +10497,7 @@
         <v>293</v>
       </c>
       <c r="F28" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -10515,7 +10547,7 @@
         <v>293</v>
       </c>
       <c r="F29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -10565,7 +10597,7 @@
         <v>293</v>
       </c>
       <c r="F30" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -10615,7 +10647,7 @@
         <v>293</v>
       </c>
       <c r="F31" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G31">
         <v>7</v>
@@ -10815,7 +10847,7 @@
         <v>296</v>
       </c>
       <c r="F35" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -10865,7 +10897,7 @@
         <v>296</v>
       </c>
       <c r="F36" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G36">
         <v>10</v>
@@ -10915,7 +10947,7 @@
         <v>296</v>
       </c>
       <c r="F37" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -10965,7 +10997,7 @@
         <v>296</v>
       </c>
       <c r="F38" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G38">
         <v>16</v>
@@ -11015,7 +11047,7 @@
         <v>296</v>
       </c>
       <c r="F39" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G39">
         <v>10</v>
@@ -11065,7 +11097,7 @@
         <v>296</v>
       </c>
       <c r="F40" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -11115,7 +11147,7 @@
         <v>297</v>
       </c>
       <c r="F41" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G41">
         <v>9</v>
@@ -11165,7 +11197,7 @@
         <v>297</v>
       </c>
       <c r="F42" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -11215,7 +11247,7 @@
         <v>297</v>
       </c>
       <c r="F43" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G43">
         <v>21</v>
@@ -12115,7 +12147,7 @@
         <v>299</v>
       </c>
       <c r="F61" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G61">
         <v>4</v>
@@ -13015,7 +13047,7 @@
         <v>301</v>
       </c>
       <c r="F79" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G79">
         <v>5</v>
@@ -14065,7 +14097,7 @@
         <v>308</v>
       </c>
       <c r="F100" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G100">
         <v>297</v>
@@ -15065,7 +15097,7 @@
         <v>313</v>
       </c>
       <c r="F120" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G120">
         <v>100</v>
@@ -16165,7 +16197,7 @@
         <v>315</v>
       </c>
       <c r="F142" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G142">
         <v>33</v>
@@ -19165,7 +19197,7 @@
         <v>331</v>
       </c>
       <c r="F202" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G202">
         <v>90</v>
@@ -19965,7 +19997,7 @@
         <v>340</v>
       </c>
       <c r="F218" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G218">
         <v>100</v>
@@ -20065,7 +20097,7 @@
         <v>342</v>
       </c>
       <c r="F220" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G220">
         <v>232</v>
@@ -20165,7 +20197,7 @@
         <v>343</v>
       </c>
       <c r="F222" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G222">
         <v>195</v>
@@ -20196,6 +20228,56 @@
       </c>
       <c r="P222">
         <v>5110</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16">
+      <c r="A223" t="s">
+        <v>268</v>
+      </c>
+      <c r="B223">
+        <v>11011476</v>
+      </c>
+      <c r="C223" t="s">
+        <v>82</v>
+      </c>
+      <c r="D223" t="s">
+        <v>287</v>
+      </c>
+      <c r="E223" t="s">
+        <v>344</v>
+      </c>
+      <c r="F223" t="s">
+        <v>360</v>
+      </c>
+      <c r="G223">
+        <v>61</v>
+      </c>
+      <c r="H223">
+        <v>8110</v>
+      </c>
+      <c r="I223">
+        <v>494710</v>
+      </c>
+      <c r="J223">
+        <v>299.3</v>
+      </c>
+      <c r="K223">
+        <v>2993</v>
+      </c>
+      <c r="L223">
+        <v>498002.3</v>
+      </c>
+      <c r="M223" t="s">
+        <v>190</v>
+      </c>
+      <c r="N223" s="1">
+        <v>46294</v>
+      </c>
+      <c r="O223" t="s">
+        <v>82</v>
+      </c>
+      <c r="P223">
+        <v>8110</v>
       </c>
     </row>
   </sheetData>
@@ -20218,15 +20300,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B2">
-        <v>1110511.68</v>
+        <v>612509.38</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B3">
         <v>1292494.146087911</v>
@@ -20234,10 +20316,10 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B4">
-        <v>1160634.330769231</v>
+        <v>528037.2307692306</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -154,133 +154,133 @@
     <t>Ganancia/Perdida NO Realizada ($)</t>
   </si>
   <si>
+    <t>YPFD</t>
+  </si>
+  <si>
+    <t>PESOS LÍQUIDOS</t>
+  </si>
+  <si>
+    <t>DÓLARES LÍQUIDOS</t>
+  </si>
+  <si>
+    <t>CABLE LÍQUIDO</t>
+  </si>
+  <si>
+    <t>Cable</t>
+  </si>
+  <si>
+    <t>Fecha Compra Origen</t>
+  </si>
+  <si>
+    <t>Fecha Venta</t>
+  </si>
+  <si>
+    <t>Precio Compra Promedio</t>
+  </si>
+  <si>
+    <t>Precio Venta Real</t>
+  </si>
+  <si>
+    <t>P&amp;L Realizado ($)</t>
+  </si>
+  <si>
+    <t>BONO REP. ARGENTINA USD STEP UP 2030</t>
+  </si>
+  <si>
+    <t>Fecha de Compra</t>
+  </si>
+  <si>
+    <t>Cantidad Viva</t>
+  </si>
+  <si>
+    <t>Precio Operado</t>
+  </si>
+  <si>
+    <t>Comisión Unitaria</t>
+  </si>
+  <si>
+    <t>Costo Real (Entrada)</t>
+  </si>
+  <si>
+    <t>Breakeven Salida</t>
+  </si>
+  <si>
+    <t>Capital Asignado</t>
+  </si>
+  <si>
+    <t>Metrica</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Comisiones Broker (Arancel)</t>
+  </si>
+  <si>
+    <t>Derechos de Mercado (Bolsa)</t>
+  </si>
+  <si>
+    <t>Total Costos Operativos</t>
+  </si>
+  <si>
+    <t>Fondeos ARS</t>
+  </si>
+  <si>
+    <t>Fondeos USD</t>
+  </si>
+  <si>
+    <t>Fondeos USD Historico ARS</t>
+  </si>
+  <si>
+    <t>Retiros ARS</t>
+  </si>
+  <si>
+    <t>Retiros USD</t>
+  </si>
+  <si>
+    <t>Retiros USD Historico ARS</t>
+  </si>
+  <si>
+    <t>Rentas ARS</t>
+  </si>
+  <si>
+    <t>Rentas USD</t>
+  </si>
+  <si>
+    <t>Rentas USD Historico ARS</t>
+  </si>
+  <si>
+    <t>Especie</t>
+  </si>
+  <si>
+    <t>Num Boleto</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Bruto</t>
+  </si>
+  <si>
+    <t>Costos Mercado</t>
+  </si>
+  <si>
+    <t>Arancel</t>
+  </si>
+  <si>
+    <t>Neto</t>
+  </si>
+  <si>
+    <t>Fecha_Norm</t>
+  </si>
+  <si>
+    <t>Ticker_Norm</t>
+  </si>
+  <si>
+    <t>Precio_Real</t>
+  </si>
+  <si>
     <t>CEDEAR GOOGLE INC.</t>
-  </si>
-  <si>
-    <t>YPFD</t>
-  </si>
-  <si>
-    <t>PESOS LÍQUIDOS</t>
-  </si>
-  <si>
-    <t>DÓLARES LÍQUIDOS</t>
-  </si>
-  <si>
-    <t>CABLE LÍQUIDO</t>
-  </si>
-  <si>
-    <t>Cable</t>
-  </si>
-  <si>
-    <t>Fecha Compra Origen</t>
-  </si>
-  <si>
-    <t>Fecha Venta</t>
-  </si>
-  <si>
-    <t>Precio Compra Promedio</t>
-  </si>
-  <si>
-    <t>Precio Venta Real</t>
-  </si>
-  <si>
-    <t>P&amp;L Realizado ($)</t>
-  </si>
-  <si>
-    <t>BONO REP. ARGENTINA USD STEP UP 2030</t>
-  </si>
-  <si>
-    <t>Fecha de Compra</t>
-  </si>
-  <si>
-    <t>Cantidad Viva</t>
-  </si>
-  <si>
-    <t>Precio Operado</t>
-  </si>
-  <si>
-    <t>Comisión Unitaria</t>
-  </si>
-  <si>
-    <t>Costo Real (Entrada)</t>
-  </si>
-  <si>
-    <t>Breakeven Salida</t>
-  </si>
-  <si>
-    <t>Capital Asignado</t>
-  </si>
-  <si>
-    <t>Metrica</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Comisiones Broker (Arancel)</t>
-  </si>
-  <si>
-    <t>Derechos de Mercado (Bolsa)</t>
-  </si>
-  <si>
-    <t>Total Costos Operativos</t>
-  </si>
-  <si>
-    <t>Fondeos ARS</t>
-  </si>
-  <si>
-    <t>Fondeos USD</t>
-  </si>
-  <si>
-    <t>Fondeos USD Historico ARS</t>
-  </si>
-  <si>
-    <t>Retiros ARS</t>
-  </si>
-  <si>
-    <t>Retiros USD</t>
-  </si>
-  <si>
-    <t>Retiros USD Historico ARS</t>
-  </si>
-  <si>
-    <t>Rentas ARS</t>
-  </si>
-  <si>
-    <t>Rentas USD</t>
-  </si>
-  <si>
-    <t>Rentas USD Historico ARS</t>
-  </si>
-  <si>
-    <t>Especie</t>
-  </si>
-  <si>
-    <t>Num Boleto</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Bruto</t>
-  </si>
-  <si>
-    <t>Costos Mercado</t>
-  </si>
-  <si>
-    <t>Arancel</t>
-  </si>
-  <si>
-    <t>Neto</t>
-  </si>
-  <si>
-    <t>Fecha_Norm</t>
-  </si>
-  <si>
-    <t>Ticker_Norm</t>
-  </si>
-  <si>
-    <t>Precio_Real</t>
   </si>
   <si>
     <t>CEDEAR NVIDIA CORPORATION</t>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -1377,13 +1377,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>6195</v>
+        <v>9595</v>
       </c>
       <c r="G2">
-        <v>37170</v>
+        <v>57570</v>
       </c>
       <c r="H2">
-        <v>-301.3300000000017</v>
+        <v>20098.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1403,18 +1403,18 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>15470</v>
+        <v>15930</v>
       </c>
       <c r="G3">
-        <v>5074160</v>
+        <v>5225040</v>
       </c>
       <c r="H3">
-        <v>1453442.89</v>
+        <v>1604322.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>121</v>
@@ -1429,18 +1429,18 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8140</v>
+        <v>7990</v>
       </c>
       <c r="G4">
-        <v>984940</v>
+        <v>966790</v>
       </c>
       <c r="H4">
-        <v>-6554.780000000144</v>
+        <v>-24704.78000000014</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>13215.43</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6">
         <v>2.66</v>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <v>2.43</v>
@@ -1504,7 +1504,7 @@
         <v>2.43</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1528,10 +1528,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
         <v>50</v>
-      </c>
-      <c r="B1" t="s">
-        <v>51</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1543,13 +1543,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>53</v>
-      </c>
-      <c r="H1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1560,7 +1560,7 @@
         <v>45667</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -1586,7 +1586,7 @@
         <v>45922</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>
@@ -1612,7 +1612,7 @@
         <v>45922</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
         <v>34</v>
@@ -1638,7 +1638,7 @@
         <v>45922</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
@@ -1664,7 +1664,7 @@
         <v>45922</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
@@ -1690,7 +1690,7 @@
         <v>45922</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
@@ -1716,7 +1716,7 @@
         <v>45922</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
@@ -1749,30 +1749,30 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>61</v>
-      </c>
-      <c r="H1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1">
         <v>45922</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1">
         <v>46294</v>
@@ -1860,15 +1860,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
         <v>63</v>
-      </c>
-      <c r="B1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2">
         <v>80858.065</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3">
         <v>3871.8</v>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4">
         <v>84729.86500000001</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <v>4000000</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B11">
         <v>-34.91</v>
@@ -1948,7 +1948,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12">
         <v>684.95</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13">
         <v>837559.262</v>
@@ -1974,16 +1974,16 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" t="s">
         <v>77</v>
-      </c>
-      <c r="B1" t="s">
-        <v>78</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1998,33 +1998,33 @@
         <v>5</v>
       </c>
       <c r="I1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" t="s">
         <v>80</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>81</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>82</v>
-      </c>
-      <c r="L1" t="s">
-        <v>83</v>
       </c>
       <c r="M1" t="s">
         <v>7</v>
       </c>
       <c r="N1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O1" t="s">
         <v>84</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>85</v>
-      </c>
-      <c r="P1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <v>9366809</v>
@@ -2066,7 +2066,7 @@
         <v>45588</v>
       </c>
       <c r="O2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P2">
         <v>719.9</v>
@@ -2074,7 +2074,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3">
         <v>10559899</v>
@@ -2116,7 +2116,7 @@
         <v>45623</v>
       </c>
       <c r="O3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P3">
         <v>764</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4">
         <v>11735210</v>
@@ -2166,7 +2166,7 @@
         <v>45656</v>
       </c>
       <c r="O4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P4">
         <v>878</v>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5">
         <v>375159</v>
@@ -2216,7 +2216,7 @@
         <v>45667</v>
       </c>
       <c r="O5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P5">
         <v>789.3</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>375160</v>
@@ -2266,7 +2266,7 @@
         <v>45667</v>
       </c>
       <c r="O6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P6">
         <v>0.6766</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7">
         <v>375161</v>
@@ -2316,7 +2316,7 @@
         <v>45667</v>
       </c>
       <c r="O7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P7">
         <v>789.1</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>6088711</v>
@@ -2366,7 +2366,7 @@
         <v>45852</v>
       </c>
       <c r="O8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P8">
         <v>0.5986</v>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="B9">
         <v>9059994</v>
@@ -2416,7 +2416,7 @@
         <v>45922</v>
       </c>
       <c r="O9" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="P9">
         <v>6195</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11">
         <v>9059996</v>
@@ -2516,7 +2516,7 @@
         <v>45922</v>
       </c>
       <c r="O11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P11">
         <v>748.5</v>
@@ -2530,7 +2530,7 @@
         <v>10990077</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
         <v>89</v>
@@ -2566,7 +2566,7 @@
         <v>46294</v>
       </c>
       <c r="O12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P12">
         <v>8140</v>
@@ -2584,10 +2584,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
         <v>63</v>
-      </c>
-      <c r="B1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2611,7 +2611,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1459802.21</v>
+        <v>1612932.21</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1377,13 +1377,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9595</v>
+        <v>9670</v>
       </c>
       <c r="G2">
-        <v>57570</v>
+        <v>58020</v>
       </c>
       <c r="H2">
-        <v>20098.67</v>
+        <v>20548.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>15930</v>
+        <v>16220</v>
       </c>
       <c r="G3">
-        <v>5225040</v>
+        <v>5320160</v>
       </c>
       <c r="H3">
-        <v>1604322.89</v>
+        <v>1699442.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>7990</v>
+        <v>8225</v>
       </c>
       <c r="G4">
-        <v>966790</v>
+        <v>995225</v>
       </c>
       <c r="H4">
-        <v>-24704.78000000014</v>
+        <v>3730.219999999856</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>13215.43</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>-13215.43</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1481,13 +1481,13 @@
         <v>36</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1507,13 +1507,13 @@
         <v>48</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>-2.43</v>
       </c>
     </row>
   </sheetData>
@@ -2611,7 +2611,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1612932.21</v>
+        <v>1723716.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -329,8 +329,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -346,7 +354,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -354,12 +362,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -659,31 +685,31 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1335,28 +1361,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1377,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9670</v>
+        <v>9675</v>
       </c>
       <c r="G2">
-        <v>58020</v>
+        <v>58050</v>
       </c>
       <c r="H2">
-        <v>20548.67</v>
+        <v>20578.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1403,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>16220</v>
+        <v>16100</v>
       </c>
       <c r="G3">
-        <v>5320160</v>
+        <v>5280800</v>
       </c>
       <c r="H3">
-        <v>1699442.89</v>
+        <v>1660082.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1429,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8225</v>
+        <v>8190</v>
       </c>
       <c r="G4">
-        <v>995225</v>
+        <v>990990</v>
       </c>
       <c r="H4">
-        <v>3730.219999999856</v>
+        <v>-504.7800000001444</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1527,36 +1553,36 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>45588</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>45667</v>
       </c>
       <c r="C2" t="s">
@@ -1579,10 +1605,10 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>45588</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>45922</v>
       </c>
       <c r="C3" t="s">
@@ -1605,10 +1631,10 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>45623</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>45922</v>
       </c>
       <c r="C4" t="s">
@@ -1631,10 +1657,10 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>45656</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>45922</v>
       </c>
       <c r="C5" t="s">
@@ -1657,10 +1683,10 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>45667</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>45922</v>
       </c>
       <c r="C6" t="s">
@@ -1683,10 +1709,10 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>45667</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>45922</v>
       </c>
       <c r="C7" t="s">
@@ -1709,10 +1735,10 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>45852</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>45922</v>
       </c>
       <c r="C8" t="s">
@@ -1745,28 +1771,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1774,7 +1800,7 @@
       <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>45922</v>
       </c>
       <c r="C2">
@@ -1800,7 +1826,7 @@
       <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>45922</v>
       </c>
       <c r="C3">
@@ -1826,7 +1852,7 @@
       <c r="A4" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>46294</v>
       </c>
       <c r="C4">
@@ -1859,10 +1885,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1973,52 +1999,52 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2062,7 +2088,7 @@
       <c r="M2" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="2">
         <v>45588</v>
       </c>
       <c r="O2" t="s">
@@ -2112,7 +2138,7 @@
       <c r="M3" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="2">
         <v>45623</v>
       </c>
       <c r="O3" t="s">
@@ -2162,7 +2188,7 @@
       <c r="M4" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N4" s="2">
         <v>45656</v>
       </c>
       <c r="O4" t="s">
@@ -2212,7 +2238,7 @@
       <c r="M5" t="s">
         <v>34</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <v>45667</v>
       </c>
       <c r="O5" t="s">
@@ -2262,7 +2288,7 @@
       <c r="M6" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <v>45667</v>
       </c>
       <c r="O6" t="s">
@@ -2312,7 +2338,7 @@
       <c r="M7" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="2">
         <v>45667</v>
       </c>
       <c r="O7" t="s">
@@ -2362,7 +2388,7 @@
       <c r="M8" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8" s="2">
         <v>45852</v>
       </c>
       <c r="O8" t="s">
@@ -2412,7 +2438,7 @@
       <c r="M9" t="s">
         <v>34</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="2">
         <v>45922</v>
       </c>
       <c r="O9" t="s">
@@ -2462,7 +2488,7 @@
       <c r="M10" t="s">
         <v>34</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="2">
         <v>45922</v>
       </c>
       <c r="O10" t="s">
@@ -2512,7 +2538,7 @@
       <c r="M11" t="s">
         <v>34</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="2">
         <v>45922</v>
       </c>
       <c r="O11" t="s">
@@ -2562,7 +2588,7 @@
       <c r="M12" t="s">
         <v>34</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <v>46294</v>
       </c>
       <c r="O12" t="s">
@@ -2583,10 +2609,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2611,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1723716.69</v>
+        <v>1680151.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8190</v>
+        <v>8245</v>
       </c>
       <c r="G4">
-        <v>990990</v>
+        <v>997645</v>
       </c>
       <c r="H4">
-        <v>-504.7800000001444</v>
+        <v>6150.219999999856</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1680151.69</v>
+        <v>1686806.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9675</v>
+        <v>9760</v>
       </c>
       <c r="G2">
-        <v>58050</v>
+        <v>58560</v>
       </c>
       <c r="H2">
-        <v>20578.67</v>
+        <v>21088.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>16100</v>
+        <v>15950</v>
       </c>
       <c r="G3">
-        <v>5280800</v>
+        <v>5231600</v>
       </c>
       <c r="H3">
-        <v>1660082.89</v>
+        <v>1610882.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8245</v>
+        <v>7980</v>
       </c>
       <c r="G4">
-        <v>997645</v>
+        <v>965580</v>
       </c>
       <c r="H4">
-        <v>6150.219999999856</v>
+        <v>-25914.78000000014</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1686806.69</v>
+        <v>1606051.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9760</v>
+        <v>9700</v>
       </c>
       <c r="G2">
-        <v>58560</v>
+        <v>58200</v>
       </c>
       <c r="H2">
-        <v>21088.67</v>
+        <v>20728.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>15950</v>
+        <v>15530</v>
       </c>
       <c r="G3">
-        <v>5231600</v>
+        <v>5093840</v>
       </c>
       <c r="H3">
-        <v>1610882.89</v>
+        <v>1473122.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>7980</v>
+        <v>8045</v>
       </c>
       <c r="G4">
-        <v>965580</v>
+        <v>973445</v>
       </c>
       <c r="H4">
-        <v>-25914.78000000014</v>
+        <v>-18049.78000000014</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1606051.69</v>
+        <v>1475796.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9700</v>
+        <v>9810</v>
       </c>
       <c r="G2">
-        <v>58200</v>
+        <v>58860</v>
       </c>
       <c r="H2">
-        <v>20728.67</v>
+        <v>21388.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>15530</v>
+        <v>15460</v>
       </c>
       <c r="G3">
-        <v>5093840</v>
+        <v>5070880</v>
       </c>
       <c r="H3">
-        <v>1473122.89</v>
+        <v>1450162.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8045</v>
+        <v>8065</v>
       </c>
       <c r="G4">
-        <v>973445</v>
+        <v>975865</v>
       </c>
       <c r="H4">
-        <v>-18049.78000000014</v>
+        <v>-15629.78000000014</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1475796.69</v>
+        <v>1455916.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9810</v>
+        <v>9870</v>
       </c>
       <c r="G2">
-        <v>58860</v>
+        <v>59220</v>
       </c>
       <c r="H2">
-        <v>21388.67</v>
+        <v>21748.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>15460</v>
+        <v>15300</v>
       </c>
       <c r="G3">
-        <v>5070880</v>
+        <v>5018400</v>
       </c>
       <c r="H3">
-        <v>1450162.89</v>
+        <v>1397682.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8065</v>
+        <v>8330</v>
       </c>
       <c r="G4">
-        <v>975865</v>
+        <v>1007930</v>
       </c>
       <c r="H4">
-        <v>-15629.78000000014</v>
+        <v>16435.21999999986</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1455916.69</v>
+        <v>1435861.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9870</v>
+        <v>9715</v>
       </c>
       <c r="G2">
-        <v>59220</v>
+        <v>58290</v>
       </c>
       <c r="H2">
-        <v>21748.67</v>
+        <v>20818.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>15300</v>
+        <v>14910</v>
       </c>
       <c r="G3">
-        <v>5018400</v>
+        <v>4890480</v>
       </c>
       <c r="H3">
-        <v>1397682.89</v>
+        <v>1269762.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8330</v>
+        <v>8460</v>
       </c>
       <c r="G4">
-        <v>1007930</v>
+        <v>1023660</v>
       </c>
       <c r="H4">
-        <v>16435.21999999986</v>
+        <v>32165.21999999986</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1435861.69</v>
+        <v>1322741.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9715</v>
+        <v>9755</v>
       </c>
       <c r="G2">
-        <v>58290</v>
+        <v>58530</v>
       </c>
       <c r="H2">
-        <v>20818.67</v>
+        <v>21058.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>14910</v>
+        <v>14660</v>
       </c>
       <c r="G3">
-        <v>4890480</v>
+        <v>4808480</v>
       </c>
       <c r="H3">
-        <v>1269762.89</v>
+        <v>1187762.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8460</v>
+        <v>8270</v>
       </c>
       <c r="G4">
-        <v>1023660</v>
+        <v>1000670</v>
       </c>
       <c r="H4">
-        <v>32165.21999999986</v>
+        <v>9175.219999999856</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1322741.69</v>
+        <v>1217991.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9755</v>
+        <v>9530</v>
       </c>
       <c r="G2">
-        <v>58530</v>
+        <v>57180</v>
       </c>
       <c r="H2">
-        <v>21058.67</v>
+        <v>19708.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>14660</v>
+        <v>14510</v>
       </c>
       <c r="G3">
-        <v>4808480</v>
+        <v>4759280</v>
       </c>
       <c r="H3">
-        <v>1187762.89</v>
+        <v>1138562.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8270</v>
+        <v>8430</v>
       </c>
       <c r="G4">
-        <v>1000670</v>
+        <v>1020030</v>
       </c>
       <c r="H4">
-        <v>9175.219999999856</v>
+        <v>28535.21999999986</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1217991.69</v>
+        <v>1186801.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9530</v>
+        <v>9670</v>
       </c>
       <c r="G2">
-        <v>57180</v>
+        <v>58020</v>
       </c>
       <c r="H2">
-        <v>19708.67</v>
+        <v>20548.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>14510</v>
+        <v>14720</v>
       </c>
       <c r="G3">
-        <v>4759280</v>
+        <v>4828160</v>
       </c>
       <c r="H3">
-        <v>1138562.89</v>
+        <v>1207442.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8430</v>
+        <v>8235</v>
       </c>
       <c r="G4">
-        <v>1020030</v>
+        <v>996435</v>
       </c>
       <c r="H4">
-        <v>28535.21999999986</v>
+        <v>4940.219999999856</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1186801.69</v>
+        <v>1232926.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9670</v>
+        <v>9550</v>
       </c>
       <c r="G2">
-        <v>58020</v>
+        <v>57300</v>
       </c>
       <c r="H2">
-        <v>20548.67</v>
+        <v>19828.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8235</v>
+        <v>8220</v>
       </c>
       <c r="G4">
-        <v>996435</v>
+        <v>994620</v>
       </c>
       <c r="H4">
-        <v>4940.219999999856</v>
+        <v>3125.219999999856</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1232926.69</v>
+        <v>1230391.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9550</v>
+        <v>9460</v>
       </c>
       <c r="G2">
-        <v>57300</v>
+        <v>56760</v>
       </c>
       <c r="H2">
-        <v>19828.67</v>
+        <v>19288.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>14720</v>
+        <v>15130</v>
       </c>
       <c r="G3">
-        <v>4828160</v>
+        <v>4962640</v>
       </c>
       <c r="H3">
-        <v>1207442.89</v>
+        <v>1341922.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8220</v>
+        <v>8240</v>
       </c>
       <c r="G4">
-        <v>994620</v>
+        <v>997040</v>
       </c>
       <c r="H4">
-        <v>3125.219999999856</v>
+        <v>5545.219999999856</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1230391.69</v>
+        <v>1366751.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9460</v>
+        <v>9135</v>
       </c>
       <c r="G2">
-        <v>56760</v>
+        <v>54810</v>
       </c>
       <c r="H2">
-        <v>19288.67</v>
+        <v>17338.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>15130</v>
+        <v>14510</v>
       </c>
       <c r="G3">
-        <v>4962640</v>
+        <v>4759280</v>
       </c>
       <c r="H3">
-        <v>1341922.89</v>
+        <v>1138562.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8240</v>
+        <v>8040</v>
       </c>
       <c r="G4">
-        <v>997040</v>
+        <v>972840</v>
       </c>
       <c r="H4">
-        <v>5545.219999999856</v>
+        <v>-18654.78000000014</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1366751.69</v>
+        <v>1137241.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9135</v>
+        <v>9140</v>
       </c>
       <c r="G2">
-        <v>54810</v>
+        <v>54840</v>
       </c>
       <c r="H2">
-        <v>17338.67</v>
+        <v>17368.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>14510</v>
+        <v>14560</v>
       </c>
       <c r="G3">
-        <v>4759280</v>
+        <v>4775680</v>
       </c>
       <c r="H3">
-        <v>1138562.89</v>
+        <v>1154962.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8040</v>
+        <v>8350</v>
       </c>
       <c r="G4">
-        <v>972840</v>
+        <v>1010350</v>
       </c>
       <c r="H4">
-        <v>-18654.78000000014</v>
+        <v>18855.21999999986</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1137241.69</v>
+        <v>1191181.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9140</v>
+        <v>9195</v>
       </c>
       <c r="G2">
-        <v>54840</v>
+        <v>55170</v>
       </c>
       <c r="H2">
-        <v>17368.67</v>
+        <v>17698.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>14560</v>
+        <v>15130</v>
       </c>
       <c r="G3">
-        <v>4775680</v>
+        <v>4962640</v>
       </c>
       <c r="H3">
-        <v>1154962.89</v>
+        <v>1341922.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8350</v>
+        <v>8260</v>
       </c>
       <c r="G4">
-        <v>1010350</v>
+        <v>999460</v>
       </c>
       <c r="H4">
-        <v>18855.21999999986</v>
+        <v>7965.219999999856</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1191181.69</v>
+        <v>1367581.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9195</v>
+        <v>9190</v>
       </c>
       <c r="G2">
-        <v>55170</v>
+        <v>55140</v>
       </c>
       <c r="H2">
-        <v>17698.67</v>
+        <v>17668.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>15130</v>
+        <v>15050</v>
       </c>
       <c r="G3">
-        <v>4962640</v>
+        <v>4936400</v>
       </c>
       <c r="H3">
-        <v>1341922.89</v>
+        <v>1315682.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8260</v>
+        <v>8030</v>
       </c>
       <c r="G4">
-        <v>999460</v>
+        <v>971630</v>
       </c>
       <c r="H4">
-        <v>7965.219999999856</v>
+        <v>-19864.78000000014</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1367581.69</v>
+        <v>1313481.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9190</v>
+        <v>9315</v>
       </c>
       <c r="G2">
-        <v>55140</v>
+        <v>55890</v>
       </c>
       <c r="H2">
-        <v>17668.67</v>
+        <v>18418.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>15050</v>
+        <v>14870</v>
       </c>
       <c r="G3">
-        <v>4936400</v>
+        <v>4877360</v>
       </c>
       <c r="H3">
-        <v>1315682.89</v>
+        <v>1256642.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8030</v>
+        <v>8185</v>
       </c>
       <c r="G4">
-        <v>971630</v>
+        <v>990385</v>
       </c>
       <c r="H4">
-        <v>-19864.78000000014</v>
+        <v>-1109.780000000144</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1313481.69</v>
+        <v>1273946.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>9315</v>
+        <v>8065</v>
       </c>
       <c r="G2">
-        <v>55890</v>
+        <v>48390</v>
       </c>
       <c r="H2">
-        <v>18418.67</v>
+        <v>10918.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>14870</v>
+        <v>14690</v>
       </c>
       <c r="G3">
-        <v>4877360</v>
+        <v>4818320</v>
       </c>
       <c r="H3">
-        <v>1256642.89</v>
+        <v>1197602.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>8185</v>
+        <v>7870</v>
       </c>
       <c r="G4">
-        <v>990385</v>
+        <v>952270</v>
       </c>
       <c r="H4">
-        <v>-1109.780000000144</v>
+        <v>-39224.78000000014</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1273946.69</v>
+        <v>1169291.69</v>
       </c>
     </row>
   </sheetData>

--- a/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
+++ b/mi_cartera_balanz/data/Reporte_Avanzado_Cartera.xlsx
@@ -1403,13 +1403,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>8065</v>
+        <v>8030</v>
       </c>
       <c r="G2">
-        <v>48390</v>
+        <v>48180</v>
       </c>
       <c r="H2">
-        <v>10918.67</v>
+        <v>10708.67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1429,13 +1429,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>14690</v>
+        <v>14180</v>
       </c>
       <c r="G3">
-        <v>4818320</v>
+        <v>4651040</v>
       </c>
       <c r="H3">
-        <v>1197602.89</v>
+        <v>1030322.89</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1455,13 +1455,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>7870</v>
+        <v>7785</v>
       </c>
       <c r="G4">
-        <v>952270</v>
+        <v>941985</v>
       </c>
       <c r="H4">
-        <v>-39224.78000000014</v>
+        <v>-49509.78000000014</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2637,7 +2637,7 @@
         <v>99</v>
       </c>
       <c r="B4">
-        <v>1169291.69</v>
+        <v>991516.6899999999</v>
       </c>
     </row>
   </sheetData>
